--- a/test/integration/03-out.xlsx
+++ b/test/integration/03-out.xlsx
@@ -15,6 +15,353 @@
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="114">
+  <si>
+    <t>variable</t>
+  </si>
+  <si>
+    <t>coefficient</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>Buğday, Durum Buğdayı Hariç</t>
+  </si>
+  <si>
+    <t>Buğday, Durum Buğdayı Hariç Satış</t>
+  </si>
+  <si>
+    <t>Buğday (Sulu)</t>
+  </si>
+  <si>
+    <t>Buğday (Sulu) Satış</t>
+  </si>
+  <si>
+    <t>Mısır (Dane)</t>
+  </si>
+  <si>
+    <t>Mısır (Dane) Satış</t>
+  </si>
+  <si>
+    <t>Arpa (Diğer) (Kuru)</t>
+  </si>
+  <si>
+    <t>Arpa (Diğer) (Kuru) Satış</t>
+  </si>
+  <si>
+    <t>Arpa (Sulu)</t>
+  </si>
+  <si>
+    <t>Arpa (Sulu) Satış</t>
+  </si>
+  <si>
+    <t>Fasulye, Taze</t>
+  </si>
+  <si>
+    <t>Fasulye, Taze Satış</t>
+  </si>
+  <si>
+    <t>Karpuz</t>
+  </si>
+  <si>
+    <t>Karpuz Satış</t>
+  </si>
+  <si>
+    <t>Kavun</t>
+  </si>
+  <si>
+    <t>Kavun Satış</t>
+  </si>
+  <si>
+    <t>Biber (Sivri)</t>
+  </si>
+  <si>
+    <t>Biber (Sivri) Satış</t>
+  </si>
+  <si>
+    <t>Hıyar (Sofralık)</t>
+  </si>
+  <si>
+    <t>Hıyar (Sofralık) Satış</t>
+  </si>
+  <si>
+    <t>Patlıcan</t>
+  </si>
+  <si>
+    <t>Patlıcan Satış</t>
+  </si>
+  <si>
+    <t>Domates (Sofralık)</t>
+  </si>
+  <si>
+    <t>Domates (Sofralık) Satış</t>
+  </si>
+  <si>
+    <t>Elma (Bütünleştirilmiş)</t>
+  </si>
+  <si>
+    <t>Elma (Bütünleştirilmiş) Satış</t>
+  </si>
+  <si>
+    <t>Armut</t>
+  </si>
+  <si>
+    <t>Armut Satış</t>
+  </si>
+  <si>
+    <t>İg1</t>
+  </si>
+  <si>
+    <t>İg2</t>
+  </si>
+  <si>
+    <t>İg3</t>
+  </si>
+  <si>
+    <t>İg4</t>
+  </si>
+  <si>
+    <t>İg5</t>
+  </si>
+  <si>
+    <t>İg6</t>
+  </si>
+  <si>
+    <t>İg7</t>
+  </si>
+  <si>
+    <t>İg8</t>
+  </si>
+  <si>
+    <t>İg9</t>
+  </si>
+  <si>
+    <t>İg10</t>
+  </si>
+  <si>
+    <t>İg11</t>
+  </si>
+  <si>
+    <t>İg12</t>
+  </si>
+  <si>
+    <t>Sermaye Temini</t>
+  </si>
+  <si>
+    <t>{}</t>
+  </si>
+  <si>
+    <t>constraint</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>relation</t>
+  </si>
+  <si>
+    <t>rhs</t>
+  </si>
+  <si>
+    <t>Toplam Arazi</t>
+  </si>
+  <si>
+    <t>&lt;=</t>
+  </si>
+  <si>
+    <t>Toplam Kuru Tarla Arazisi</t>
+  </si>
+  <si>
+    <t>Toplam Sulu Tarla Arazisi</t>
+  </si>
+  <si>
+    <t>Toplam Meyve Arazisi</t>
+  </si>
+  <si>
+    <t>Toplam Sebze Arazisi</t>
+  </si>
+  <si>
+    <t>Toplam Örtü Altı Arazisi</t>
+  </si>
+  <si>
+    <t>=</t>
+  </si>
+  <si>
+    <t>Toplam Süs Bitkisi Arazisi</t>
+  </si>
+  <si>
+    <t>Buğday, Durum Buğdayı Hariç Arazisi</t>
+  </si>
+  <si>
+    <t>Buğday (Sulu) Arazisi</t>
+  </si>
+  <si>
+    <t>Mısır (Dane) Arazisi</t>
+  </si>
+  <si>
+    <t>Arpa (Diğer) (Kuru) Arazisi</t>
+  </si>
+  <si>
+    <t>Arpa (Sulu) Arazisi</t>
+  </si>
+  <si>
+    <t>Fasulye, Taze Arazisi</t>
+  </si>
+  <si>
+    <t>Karpuz Arazisi</t>
+  </si>
+  <si>
+    <t>Kavun Arazisi</t>
+  </si>
+  <si>
+    <t>Biber (Sivri) Arazisi</t>
+  </si>
+  <si>
+    <t>Hıyar (Sofralık) Arazisi</t>
+  </si>
+  <si>
+    <t>Patlıcan Arazisi</t>
+  </si>
+  <si>
+    <t>Domates (Sofralık) Arazisi</t>
+  </si>
+  <si>
+    <t>Elma (Bütünleştirilmiş) Arazisi</t>
+  </si>
+  <si>
+    <t>Armut Arazisi</t>
+  </si>
+  <si>
+    <t>Buğday, Durum Buğdayı Hariç Transfer</t>
+  </si>
+  <si>
+    <t>Buğday (Sulu) Transfer</t>
+  </si>
+  <si>
+    <t>Mısır (Dane) Transfer</t>
+  </si>
+  <si>
+    <t>Arpa (Diğer) (Kuru) Transfer</t>
+  </si>
+  <si>
+    <t>Arpa (Sulu) Transfer</t>
+  </si>
+  <si>
+    <t>Fasulye, Taze Transfer</t>
+  </si>
+  <si>
+    <t>Karpuz Transfer</t>
+  </si>
+  <si>
+    <t>Kavun Transfer</t>
+  </si>
+  <si>
+    <t>Biber (Sivri) Transfer</t>
+  </si>
+  <si>
+    <t>Hıyar (Sofralık) Transfer</t>
+  </si>
+  <si>
+    <t>Patlıcan Transfer</t>
+  </si>
+  <si>
+    <t>Domates (Sofralık) Transfer</t>
+  </si>
+  <si>
+    <t>Elma (Bütünleştirilmiş) Transfer</t>
+  </si>
+  <si>
+    <t>Armut Transfer</t>
+  </si>
+  <si>
+    <t>İşgücü Ocak</t>
+  </si>
+  <si>
+    <t>İşgücü Şubat</t>
+  </si>
+  <si>
+    <t>İşgücü Mart</t>
+  </si>
+  <si>
+    <t>İşgücü Nisan</t>
+  </si>
+  <si>
+    <t>İşgücü Mayıs</t>
+  </si>
+  <si>
+    <t>İşgücü Haziran</t>
+  </si>
+  <si>
+    <t>İşgücü Temmuz</t>
+  </si>
+  <si>
+    <t>İşgücü Ağustos</t>
+  </si>
+  <si>
+    <t>İşgücü Eylül</t>
+  </si>
+  <si>
+    <t>İşgücü Ekim</t>
+  </si>
+  <si>
+    <t>İşgücü Kasım</t>
+  </si>
+  <si>
+    <t>İşgücü Aralık</t>
+  </si>
+  <si>
+    <t>İşletme Sermayesi</t>
+  </si>
+  <si>
+    <t>Ahır Yeri</t>
+  </si>
+  <si>
+    <t>Ağıl Yeri</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>OPTIMAL</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>Solution is optimal</t>
+  </si>
+  <si>
+    <t>reduced_cost</t>
+  </si>
+  <si>
+    <t>original_value</t>
+  </si>
+  <si>
+    <t>lower_bound</t>
+  </si>
+  <si>
+    <t>upper_bound</t>
+  </si>
+  <si>
+    <t>is_basic_variable</t>
+  </si>
+  <si>
+    <t>shadow_price</t>
+  </si>
+  <si>
+    <t>slack_or_surplus</t>
+  </si>
+  <si>
+    <t>neither_bounds_are_binding</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -344,430 +691,351 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="10.5703125" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>variable</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>coefficient</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Buğday, Durum Buğdayı Hariç</t>
-        </is>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
       </c>
       <c r="B2">
         <v>-324.12</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Buğday, Durum Buğdayı Hariç Satış</t>
-        </is>
+      <c r="C2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>4</v>
       </c>
       <c r="B3">
         <v>2.73</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Buğday (Sulu)</t>
-        </is>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>5</v>
       </c>
       <c r="B4">
         <v>-839.12</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Buğday (Sulu) Satış</t>
-        </is>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>6</v>
       </c>
       <c r="B5">
         <v>2.73</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Mısır (Dane)</t>
-        </is>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>7</v>
       </c>
       <c r="B6">
         <v>-1439.82</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Mısır (Dane) Satış</t>
-        </is>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>8</v>
       </c>
       <c r="B7">
         <v>2.6</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Arpa (Diğer) (Kuru)</t>
-        </is>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>9</v>
       </c>
       <c r="B8">
         <v>-292.92</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Arpa (Diğer) (Kuru) Satış</t>
-        </is>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>10</v>
       </c>
       <c r="B9">
         <v>2.5</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Arpa (Sulu)</t>
-        </is>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>11</v>
       </c>
       <c r="B10">
         <v>-721.12</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Arpa (Sulu) Satış</t>
-        </is>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>12</v>
       </c>
       <c r="B11">
         <v>2.5</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fasulye, Taze</t>
-        </is>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>13</v>
       </c>
       <c r="B12">
         <v>-1935.27</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Fasulye, Taze Satış</t>
-        </is>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>14</v>
       </c>
       <c r="B13">
         <v>2.5</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Karpuz</t>
-        </is>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>15</v>
       </c>
       <c r="B14">
         <v>-2710.05</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Karpuz Satış</t>
-        </is>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>16</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Kavun</t>
-        </is>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>17</v>
       </c>
       <c r="B16">
         <v>-2166.68</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Kavun Satış</t>
-        </is>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>18</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Biber (Sivri)</t>
-        </is>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
+        <v>19</v>
       </c>
       <c r="B18">
         <v>-8502.950000000001</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Biber (Sivri) Satış</t>
-        </is>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>20</v>
       </c>
       <c r="B19">
         <v>2.3</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Hıyar (Sofralık)</t>
-        </is>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>21</v>
       </c>
       <c r="B20">
         <v>-5892.95</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Hıyar (Sofralık) Satış</t>
-        </is>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>22</v>
       </c>
       <c r="B21">
         <v>2.6</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Patlıcan</t>
-        </is>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>23</v>
       </c>
       <c r="B22">
         <v>-7597.45</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Patlıcan Satış</t>
-        </is>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>24</v>
       </c>
       <c r="B23">
         <v>2.2</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Domates (Sofralık)</t>
-        </is>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>25</v>
       </c>
       <c r="B24">
         <v>-6173.95</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Domates (Sofralık) Satış</t>
-        </is>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>26</v>
       </c>
       <c r="B25">
         <v>1.7</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Elma (Bütünleştirilmiş)</t>
-        </is>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>27</v>
       </c>
       <c r="B26">
         <v>-3040</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Elma (Bütünleştirilmiş) Satış</t>
-        </is>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>28</v>
       </c>
       <c r="B27">
         <v>2.3</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Armut</t>
-        </is>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>29</v>
       </c>
       <c r="B28">
         <v>-1004.65</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Armut Satış</t>
-        </is>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>30</v>
       </c>
       <c r="B29">
         <v>4</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>İg1</t>
-        </is>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>31</v>
       </c>
       <c r="B30">
         <v>-18.75</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>İg2</t>
-        </is>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>32</v>
       </c>
       <c r="B31">
         <v>-18.75</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>İg3</t>
-        </is>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>33</v>
       </c>
       <c r="B32">
         <v>-18.75</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>İg4</t>
-        </is>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>34</v>
       </c>
       <c r="B33">
         <v>-18.75</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>İg5</t>
-        </is>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>35</v>
       </c>
       <c r="B34">
         <v>-18.75</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>İg6</t>
-        </is>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>36</v>
       </c>
       <c r="B35">
         <v>-18.75</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>İg7</t>
-        </is>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>37</v>
       </c>
       <c r="B36">
         <v>-18.75</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>İg8</t>
-        </is>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>38</v>
       </c>
       <c r="B37">
         <v>-18.75</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>İg9</t>
-        </is>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>39</v>
       </c>
       <c r="B38">
         <v>-18.75</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>İg10</t>
-        </is>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>40</v>
       </c>
       <c r="B39">
         <v>-18.75</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>İg11</t>
-        </is>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>41</v>
       </c>
       <c r="B40">
         <v>-18.75</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>İg12</t>
-        </is>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>42</v>
       </c>
       <c r="B41">
         <v>-18.75</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Sermaye Temini</t>
-        </is>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
+        <v>43</v>
       </c>
       <c r="B42">
         <v>-0.25</v>
@@ -780,41 +1048,41 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AR51"/>
+  <dimension ref="A1:AS51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.5703125" customWidth="1"/>
-    <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="3" width="3.5703125" customWidth="1"/>
-    <col min="4" max="4" width="24.7109375" customWidth="1"/>
-    <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" customWidth="1"/>
-    <col min="7" max="7" width="17.5703125" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" customWidth="1"/>
-    <col min="9" max="9" width="16.7109375" customWidth="1"/>
-    <col min="10" max="10" width="17.5703125" customWidth="1"/>
-    <col min="11" max="11" width="22.85546875" customWidth="1"/>
-    <col min="12" max="12" width="10.5703125" customWidth="1"/>
-    <col min="13" max="13" width="15.85546875" customWidth="1"/>
-    <col min="14" max="14" width="12.28515625" customWidth="1"/>
-    <col min="15" max="15" width="17.5703125" customWidth="1"/>
-    <col min="16" max="16" width="6.140625" customWidth="1"/>
-    <col min="17" max="17" width="11.42578125" customWidth="1"/>
-    <col min="18" max="18" width="5.28515625" customWidth="1"/>
-    <col min="19" max="19" width="10.5703125" customWidth="1"/>
-    <col min="20" max="20" width="12.28515625" customWidth="1"/>
-    <col min="21" max="21" width="17.5703125" customWidth="1"/>
-    <col min="22" max="22" width="15" customWidth="1"/>
-    <col min="23" max="23" width="20.28515625" customWidth="1"/>
-    <col min="24" max="24" width="8" customWidth="1"/>
-    <col min="25" max="25" width="13.28515625" customWidth="1"/>
-    <col min="26" max="26" width="16.7109375" customWidth="1"/>
-    <col min="27" max="27" width="22" customWidth="1"/>
-    <col min="28" max="28" width="21.140625" customWidth="1"/>
-    <col min="29" max="29" width="26.42578125" customWidth="1"/>
-    <col min="30" max="30" width="5.28515625" customWidth="1"/>
-    <col min="31" max="31" width="10.5703125" customWidth="1"/>
-    <col min="32" max="32" width="3.5703125" customWidth="1"/>
+    <col min="2" max="2" width="2.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="3.5703125" customWidth="1"/>
+    <col min="5" max="5" width="24.7109375" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" customWidth="1"/>
+    <col min="8" max="8" width="17.5703125" customWidth="1"/>
+    <col min="9" max="9" width="11.42578125" customWidth="1"/>
+    <col min="10" max="10" width="16.7109375" customWidth="1"/>
+    <col min="11" max="11" width="17.5703125" customWidth="1"/>
+    <col min="12" max="12" width="22.85546875" customWidth="1"/>
+    <col min="13" max="13" width="10.5703125" customWidth="1"/>
+    <col min="14" max="14" width="15.85546875" customWidth="1"/>
+    <col min="15" max="15" width="12.28515625" customWidth="1"/>
+    <col min="16" max="16" width="17.5703125" customWidth="1"/>
+    <col min="17" max="17" width="6.140625" customWidth="1"/>
+    <col min="18" max="18" width="11.42578125" customWidth="1"/>
+    <col min="19" max="19" width="5.28515625" customWidth="1"/>
+    <col min="20" max="20" width="10.5703125" customWidth="1"/>
+    <col min="21" max="21" width="12.28515625" customWidth="1"/>
+    <col min="22" max="22" width="17.5703125" customWidth="1"/>
+    <col min="23" max="23" width="15" customWidth="1"/>
+    <col min="24" max="24" width="20.28515625" customWidth="1"/>
+    <col min="25" max="25" width="8" customWidth="1"/>
+    <col min="26" max="26" width="13.28515625" customWidth="1"/>
+    <col min="27" max="27" width="16.7109375" customWidth="1"/>
+    <col min="28" max="28" width="22" customWidth="1"/>
+    <col min="29" max="29" width="21.140625" customWidth="1"/>
+    <col min="30" max="30" width="26.42578125" customWidth="1"/>
+    <col min="31" max="31" width="5.28515625" customWidth="1"/>
+    <col min="32" max="32" width="10.5703125" customWidth="1"/>
     <col min="33" max="33" width="3.5703125" customWidth="1"/>
     <col min="34" max="34" width="3.5703125" customWidth="1"/>
     <col min="35" max="35" width="3.5703125" customWidth="1"/>
@@ -823,331 +1091,240 @@
     <col min="38" max="38" width="3.5703125" customWidth="1"/>
     <col min="39" max="39" width="3.5703125" customWidth="1"/>
     <col min="40" max="40" width="3.5703125" customWidth="1"/>
-    <col min="41" max="41" width="4.42578125" customWidth="1"/>
+    <col min="41" max="41" width="3.5703125" customWidth="1"/>
     <col min="42" max="42" width="4.42578125" customWidth="1"/>
     <col min="43" max="43" width="4.42578125" customWidth="1"/>
-    <col min="44" max="44" width="13.28515625" customWidth="1"/>
+    <col min="44" max="44" width="4.42578125" customWidth="1"/>
+    <col min="45" max="45" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>constraint</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>relation</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>rhs</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Buğday, Durum Buğdayı Hariç</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Buğday, Durum Buğdayı Hariç Satış</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Buğday (Sulu)</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Buğday (Sulu) Satış</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Mısır (Dane)</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Mısır (Dane) Satış</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Arpa (Diğer) (Kuru)</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Arpa (Diğer) (Kuru) Satış</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Arpa (Sulu)</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Arpa (Sulu) Satış</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Fasulye, Taze</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Fasulye, Taze Satış</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Karpuz</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Karpuz Satış</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Kavun</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>Kavun Satış</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>Biber (Sivri)</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Biber (Sivri) Satış</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>Hıyar (Sofralık)</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>Hıyar (Sofralık) Satış</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>Patlıcan</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>Patlıcan Satış</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>Domates (Sofralık)</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>Domates (Sofralık) Satış</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>Elma (Bütünleştirilmiş)</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>Elma (Bütünleştirilmiş) Satış</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>Armut</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>Armut Satış</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>İg1</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>İg2</t>
-        </is>
-      </c>
-      <c r="AH1" t="inlineStr">
-        <is>
-          <t>İg3</t>
-        </is>
-      </c>
-      <c r="AI1" t="inlineStr">
-        <is>
-          <t>İg4</t>
-        </is>
-      </c>
-      <c r="AJ1" t="inlineStr">
-        <is>
-          <t>İg5</t>
-        </is>
-      </c>
-      <c r="AK1" t="inlineStr">
-        <is>
-          <t>İg6</t>
-        </is>
-      </c>
-      <c r="AL1" t="inlineStr">
-        <is>
-          <t>İg7</t>
-        </is>
-      </c>
-      <c r="AM1" t="inlineStr">
-        <is>
-          <t>İg8</t>
-        </is>
-      </c>
-      <c r="AN1" t="inlineStr">
-        <is>
-          <t>İg9</t>
-        </is>
-      </c>
-      <c r="AO1" t="inlineStr">
-        <is>
-          <t>İg10</t>
-        </is>
-      </c>
-      <c r="AP1" t="inlineStr">
-        <is>
-          <t>İg11</t>
-        </is>
-      </c>
-      <c r="AQ1" t="inlineStr">
-        <is>
-          <t>İg12</t>
-        </is>
-      </c>
-      <c r="AR1" t="inlineStr">
-        <is>
-          <t>Sermaye Temini</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Toplam Arazi</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C2">
+    <row r="1" spans="1:45">
+      <c r="A1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" t="s">
+        <v>21</v>
+      </c>
+      <c r="X1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:45">
+      <c r="A2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2">
         <v>5508331</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2">
         <v>0</v>
@@ -1188,26 +1365,22 @@
       <c r="AR2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Toplam Kuru Tarla Arazisi</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C3">
-        <v>0</v>
+      <c r="AS2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:45">
+      <c r="A3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" t="s">
+        <v>50</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1222,10 +1395,10 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
         <v>0</v>
@@ -1326,20 +1499,16 @@
       <c r="AR3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Toplam Sulu Tarla Arazisi</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C4">
-        <v>0</v>
+      <c r="AS3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:45">
+      <c r="A4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" t="s">
+        <v>50</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -1348,16 +1517,16 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1366,10 +1535,10 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -1464,24 +1633,20 @@
       <c r="AR4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Toplam Meyve Arazisi</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C5">
+      <c r="AS4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:45">
+      <c r="A5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5">
         <v>154013</v>
       </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
       <c r="E5">
         <v>0</v>
       </c>
@@ -1552,16 +1717,16 @@
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF5">
         <v>0</v>
@@ -1602,24 +1767,20 @@
       <c r="AR5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Toplam Sebze Arazisi</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C6">
+      <c r="AS5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:45">
+      <c r="A6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6">
         <v>397158</v>
       </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
       <c r="E6">
         <v>0</v>
       </c>
@@ -1648,46 +1809,46 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB6">
         <v>0</v>
@@ -1740,20 +1901,16 @@
       <c r="AR6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Toplam Örtü Altı Arazisi</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="C7">
-        <v>0</v>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:45">
+      <c r="A7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" t="s">
+        <v>56</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1878,20 +2035,16 @@
       <c r="AR7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Toplam Süs Bitkisi Arazisi</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C8">
-        <v>0</v>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:45">
+      <c r="A8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" t="s">
+        <v>50</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -2016,26 +2169,22 @@
       <c r="AR8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Buğday, Durum Buğdayı Hariç Arazisi</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C9">
+      <c r="AS8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:45">
+      <c r="A9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9">
         <v>2189475</v>
       </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
       <c r="E9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9">
         <v>0</v>
@@ -2154,32 +2303,28 @@
       <c r="AR9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Buğday (Sulu) Arazisi</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C10">
+      <c r="AS9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:45">
+      <c r="A10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10">
         <v>279382.5</v>
       </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -2292,24 +2437,20 @@
       <c r="AR10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Mısır (Dane) Arazisi</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C11">
+      <c r="AS10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:45">
+      <c r="A11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11">
         <v>13156.5</v>
       </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
       <c r="E11">
         <v>0</v>
       </c>
@@ -2320,10 +2461,10 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -2430,24 +2571,20 @@
       <c r="AR11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Arpa (Diğer) (Kuru) Arazisi</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C12">
+      <c r="AS11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:45">
+      <c r="A12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12">
         <v>1359679.5</v>
       </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
       <c r="E12">
         <v>0</v>
       </c>
@@ -2464,10 +2601,10 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -2568,24 +2705,20 @@
       <c r="AR12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Arpa (Sulu) Arazisi</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C13">
+      <c r="AS12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:45">
+      <c r="A13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13">
         <v>87864</v>
       </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
       <c r="E13">
         <v>0</v>
       </c>
@@ -2608,10 +2741,10 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -2706,24 +2839,20 @@
       <c r="AR13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fasulye, Taze Arazisi</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C14">
+      <c r="AS13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:45">
+      <c r="A14" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14">
         <v>1962</v>
       </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
       <c r="E14">
         <v>0</v>
       </c>
@@ -2752,10 +2881,10 @@
         <v>0</v>
       </c>
       <c r="N14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -2844,24 +2973,20 @@
       <c r="AR14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Karpuz Arazisi</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C15">
+      <c r="AS14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:45">
+      <c r="A15" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15">
         <v>4992</v>
       </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
       <c r="E15">
         <v>0</v>
       </c>
@@ -2896,10 +3021,10 @@
         <v>0</v>
       </c>
       <c r="P15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -2982,24 +3107,20 @@
       <c r="AR15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Kavun Arazisi</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C16">
+      <c r="AS15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:45">
+      <c r="A16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16">
         <v>1614</v>
       </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
       <c r="E16">
         <v>0</v>
       </c>
@@ -3040,10 +3161,10 @@
         <v>0</v>
       </c>
       <c r="R16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T16">
         <v>0</v>
@@ -3120,24 +3241,20 @@
       <c r="AR16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Biber (Sivri) Arazisi</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C17">
+      <c r="AS16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:45">
+      <c r="A17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17">
         <v>922.9</v>
       </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
       <c r="E17">
         <v>0</v>
       </c>
@@ -3184,10 +3301,10 @@
         <v>0</v>
       </c>
       <c r="T17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17">
         <v>0</v>
@@ -3258,24 +3375,20 @@
       <c r="AR17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Hıyar (Sofralık) Arazisi</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C18">
+      <c r="AS17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:45">
+      <c r="A18" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18">
         <v>1101.1</v>
       </c>
-      <c r="D18">
-        <v>0</v>
-      </c>
       <c r="E18">
         <v>0</v>
       </c>
@@ -3328,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="V18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X18">
         <v>0</v>
@@ -3396,24 +3509,20 @@
       <c r="AR18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Patlıcan Arazisi</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C19">
+      <c r="AS18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:45">
+      <c r="A19" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" t="s">
+        <v>50</v>
+      </c>
+      <c r="D19">
         <v>957</v>
       </c>
-      <c r="D19">
-        <v>0</v>
-      </c>
       <c r="E19">
         <v>0</v>
       </c>
@@ -3472,10 +3581,10 @@
         <v>0</v>
       </c>
       <c r="X19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3534,24 +3643,20 @@
       <c r="AR19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Domates (Sofralık) Arazisi</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C20">
+      <c r="AS19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:45">
+      <c r="A20" t="s">
+        <v>69</v>
+      </c>
+      <c r="C20" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20">
         <v>12311.2</v>
       </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
       <c r="E20">
         <v>0</v>
       </c>
@@ -3616,10 +3721,10 @@
         <v>0</v>
       </c>
       <c r="Z20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB20">
         <v>0</v>
@@ -3672,24 +3777,20 @@
       <c r="AR20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Elma (Bütünleştirilmiş) Arazisi</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C21">
+      <c r="AS20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:45">
+      <c r="A21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21">
         <v>72783</v>
       </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
       <c r="E21">
         <v>0</v>
       </c>
@@ -3760,10 +3861,10 @@
         <v>0</v>
       </c>
       <c r="AB21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD21">
         <v>0</v>
@@ -3810,24 +3911,20 @@
       <c r="AR21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Armut Arazisi</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C22">
+      <c r="AS21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:45">
+      <c r="A22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22">
         <v>686</v>
       </c>
-      <c r="D22">
-        <v>0</v>
-      </c>
       <c r="E22">
         <v>0</v>
       </c>
@@ -3904,10 +4001,10 @@
         <v>0</v>
       </c>
       <c r="AD22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF22">
         <v>0</v>
@@ -3948,29 +4045,25 @@
       <c r="AR22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Buğday, Durum Buğdayı Hariç Transfer</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C23">
-        <v>0</v>
+      <c r="AS22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:45">
+      <c r="A23" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23" t="s">
+        <v>50</v>
       </c>
       <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
         <v>-185</v>
       </c>
-      <c r="E23">
-        <v>1</v>
-      </c>
       <c r="F23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -4086,20 +4179,16 @@
       <c r="AR23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Buğday (Sulu) Transfer</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C24">
-        <v>0</v>
+      <c r="AS23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:45">
+      <c r="A24" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" t="s">
+        <v>50</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -4108,13 +4197,13 @@
         <v>0</v>
       </c>
       <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
         <v>-436</v>
       </c>
-      <c r="G24">
-        <v>1</v>
-      </c>
       <c r="H24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -4224,20 +4313,16 @@
       <c r="AR24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Mısır (Dane) Transfer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C25">
-        <v>0</v>
+      <c r="AS24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:45">
+      <c r="A25" t="s">
+        <v>74</v>
+      </c>
+      <c r="C25" t="s">
+        <v>50</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -4252,13 +4337,13 @@
         <v>0</v>
       </c>
       <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
         <v>-1400</v>
       </c>
-      <c r="I25">
-        <v>1</v>
-      </c>
       <c r="J25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25">
         <v>0</v>
@@ -4362,20 +4447,16 @@
       <c r="AR25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Arpa (Diğer) (Kuru) Transfer</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C26">
-        <v>0</v>
+      <c r="AS25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:45">
+      <c r="A26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C26" t="s">
+        <v>50</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -4396,13 +4477,13 @@
         <v>0</v>
       </c>
       <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
         <v>-188</v>
       </c>
-      <c r="K26">
-        <v>1</v>
-      </c>
       <c r="L26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M26">
         <v>0</v>
@@ -4500,20 +4581,16 @@
       <c r="AR26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Arpa (Sulu) Transfer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C27">
-        <v>0</v>
+      <c r="AS26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:45">
+      <c r="A27" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" t="s">
+        <v>50</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -4540,13 +4617,13 @@
         <v>0</v>
       </c>
       <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
         <v>-466</v>
       </c>
-      <c r="M27">
-        <v>1</v>
-      </c>
       <c r="N27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27">
         <v>0</v>
@@ -4638,20 +4715,16 @@
       <c r="AR27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Fasulye, Taze Transfer</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C28">
-        <v>0</v>
+      <c r="AS27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:45">
+      <c r="A28" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" t="s">
+        <v>50</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -4684,13 +4757,13 @@
         <v>0</v>
       </c>
       <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28">
         <v>-1145</v>
       </c>
-      <c r="O28">
-        <v>1</v>
-      </c>
       <c r="P28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -4776,20 +4849,16 @@
       <c r="AR28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Karpuz Transfer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C29">
-        <v>0</v>
+      <c r="AS28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:45">
+      <c r="A29" t="s">
+        <v>78</v>
+      </c>
+      <c r="C29" t="s">
+        <v>50</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -4828,13 +4897,13 @@
         <v>0</v>
       </c>
       <c r="P29">
+        <v>0</v>
+      </c>
+      <c r="Q29">
         <v>-4000</v>
       </c>
-      <c r="Q29">
-        <v>1</v>
-      </c>
       <c r="R29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29">
         <v>0</v>
@@ -4914,20 +4983,16 @@
       <c r="AR29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Kavun Transfer</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C30">
-        <v>0</v>
+      <c r="AS29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:45">
+      <c r="A30" t="s">
+        <v>79</v>
+      </c>
+      <c r="C30" t="s">
+        <v>50</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -4972,13 +5037,13 @@
         <v>0</v>
       </c>
       <c r="R30">
+        <v>0</v>
+      </c>
+      <c r="S30">
         <v>-2900</v>
       </c>
-      <c r="S30">
-        <v>1</v>
-      </c>
       <c r="T30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U30">
         <v>0</v>
@@ -5052,20 +5117,16 @@
       <c r="AR30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Biber (Sivri) Transfer</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C31">
-        <v>0</v>
+      <c r="AS30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:45">
+      <c r="A31" t="s">
+        <v>80</v>
+      </c>
+      <c r="C31" t="s">
+        <v>50</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -5116,13 +5177,13 @@
         <v>0</v>
       </c>
       <c r="T31">
+        <v>0</v>
+      </c>
+      <c r="U31">
         <v>-6000</v>
       </c>
-      <c r="U31">
-        <v>1</v>
-      </c>
       <c r="V31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W31">
         <v>0</v>
@@ -5190,20 +5251,16 @@
       <c r="AR31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Hıyar (Sofralık) Transfer</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C32">
-        <v>0</v>
+      <c r="AS31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:45">
+      <c r="A32" t="s">
+        <v>81</v>
+      </c>
+      <c r="C32" t="s">
+        <v>50</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -5260,13 +5317,13 @@
         <v>0</v>
       </c>
       <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
         <v>-4500</v>
       </c>
-      <c r="W32">
-        <v>1</v>
-      </c>
       <c r="X32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y32">
         <v>0</v>
@@ -5328,20 +5385,16 @@
       <c r="AR32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Patlıcan Transfer</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C33">
-        <v>0</v>
+      <c r="AS32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:45">
+      <c r="A33" t="s">
+        <v>82</v>
+      </c>
+      <c r="C33" t="s">
+        <v>50</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -5404,13 +5457,13 @@
         <v>0</v>
       </c>
       <c r="X33">
+        <v>0</v>
+      </c>
+      <c r="Y33">
         <v>-4500</v>
       </c>
-      <c r="Y33">
-        <v>1</v>
-      </c>
       <c r="Z33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA33">
         <v>0</v>
@@ -5466,20 +5519,16 @@
       <c r="AR33">
         <v>0</v>
       </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Domates (Sofralık) Transfer</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C34">
-        <v>0</v>
+      <c r="AS33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:45">
+      <c r="A34" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34" t="s">
+        <v>50</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -5548,13 +5597,13 @@
         <v>0</v>
       </c>
       <c r="Z34">
+        <v>0</v>
+      </c>
+      <c r="AA34">
         <v>-5078</v>
       </c>
-      <c r="AA34">
-        <v>1</v>
-      </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC34">
         <v>0</v>
@@ -5604,20 +5653,16 @@
       <c r="AR34">
         <v>0</v>
       </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Elma (Bütünleştirilmiş) Transfer</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C35">
-        <v>0</v>
+      <c r="AS34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:45">
+      <c r="A35" t="s">
+        <v>84</v>
+      </c>
+      <c r="C35" t="s">
+        <v>50</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -5692,13 +5737,13 @@
         <v>0</v>
       </c>
       <c r="AB35">
+        <v>0</v>
+      </c>
+      <c r="AC35">
         <v>-3000</v>
       </c>
-      <c r="AC35">
-        <v>1</v>
-      </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE35">
         <v>0</v>
@@ -5742,20 +5787,16 @@
       <c r="AR35">
         <v>0</v>
       </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Armut Transfer</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C36">
-        <v>0</v>
+      <c r="AS35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:45">
+      <c r="A36" t="s">
+        <v>85</v>
+      </c>
+      <c r="C36" t="s">
+        <v>50</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -5836,13 +5877,13 @@
         <v>0</v>
       </c>
       <c r="AD36">
+        <v>0</v>
+      </c>
+      <c r="AE36">
         <v>-980</v>
       </c>
-      <c r="AE36">
-        <v>1</v>
-      </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG36">
         <v>0</v>
@@ -5880,24 +5921,20 @@
       <c r="AR36">
         <v>0</v>
       </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>İşgücü Ocak</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C37">
+      <c r="AS36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:45">
+      <c r="A37" t="s">
+        <v>86</v>
+      </c>
+      <c r="C37" t="s">
+        <v>50</v>
+      </c>
+      <c r="D37">
         <v>28727.4</v>
       </c>
-      <c r="D37">
-        <v>0</v>
-      </c>
       <c r="E37">
         <v>0</v>
       </c>
@@ -5980,11 +6017,11 @@
         <v>0</v>
       </c>
       <c r="AF37">
+        <v>0</v>
+      </c>
+      <c r="AG37">
         <v>-1</v>
       </c>
-      <c r="AG37">
-        <v>0</v>
-      </c>
       <c r="AH37">
         <v>0</v>
       </c>
@@ -6018,24 +6055,20 @@
       <c r="AR37">
         <v>0</v>
       </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>İşgücü Şubat</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C38">
+      <c r="AS37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:45">
+      <c r="A38" t="s">
+        <v>87</v>
+      </c>
+      <c r="C38" t="s">
+        <v>50</v>
+      </c>
+      <c r="D38">
         <v>28727.4</v>
       </c>
-      <c r="D38">
-        <v>0</v>
-      </c>
       <c r="E38">
         <v>0</v>
       </c>
@@ -6082,17 +6115,17 @@
         <v>0</v>
       </c>
       <c r="T38">
+        <v>0</v>
+      </c>
+      <c r="U38">
         <v>4.39</v>
       </c>
-      <c r="U38">
-        <v>0</v>
-      </c>
       <c r="V38">
+        <v>0</v>
+      </c>
+      <c r="W38">
         <v>4.31</v>
       </c>
-      <c r="W38">
-        <v>0</v>
-      </c>
       <c r="X38">
         <v>0</v>
       </c>
@@ -6100,32 +6133,32 @@
         <v>0</v>
       </c>
       <c r="Z38">
+        <v>0</v>
+      </c>
+      <c r="AA38">
         <v>0.5</v>
       </c>
-      <c r="AA38">
-        <v>0</v>
-      </c>
       <c r="AB38">
+        <v>0</v>
+      </c>
+      <c r="AC38">
         <v>1.67</v>
       </c>
-      <c r="AC38">
-        <v>0</v>
-      </c>
       <c r="AD38">
+        <v>0</v>
+      </c>
+      <c r="AE38">
         <v>2.9</v>
       </c>
-      <c r="AE38">
-        <v>0</v>
-      </c>
       <c r="AF38">
         <v>0</v>
       </c>
       <c r="AG38">
+        <v>0</v>
+      </c>
+      <c r="AH38">
         <v>-1</v>
       </c>
-      <c r="AH38">
-        <v>0</v>
-      </c>
       <c r="AI38">
         <v>0</v>
       </c>
@@ -6156,27 +6189,23 @@
       <c r="AR38">
         <v>0</v>
       </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>İşgücü Mart</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C39">
+      <c r="AS38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:45">
+      <c r="A39" t="s">
+        <v>88</v>
+      </c>
+      <c r="C39" t="s">
+        <v>50</v>
+      </c>
+      <c r="D39">
         <v>33796.94</v>
       </c>
-      <c r="D39">
+      <c r="E39">
         <v>0.18</v>
       </c>
-      <c r="E39">
-        <v>0</v>
-      </c>
       <c r="F39">
         <v>0</v>
       </c>
@@ -6184,29 +6213,29 @@
         <v>0</v>
       </c>
       <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
         <v>1.23</v>
       </c>
-      <c r="I39">
-        <v>0</v>
-      </c>
       <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
         <v>0.58</v>
       </c>
-      <c r="K39">
-        <v>0</v>
-      </c>
       <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
         <v>0.58</v>
       </c>
-      <c r="M39">
-        <v>0</v>
-      </c>
       <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
         <v>22.06</v>
       </c>
-      <c r="O39">
-        <v>0</v>
-      </c>
       <c r="P39">
         <v>0</v>
       </c>
@@ -6220,41 +6249,41 @@
         <v>0</v>
       </c>
       <c r="T39">
+        <v>0</v>
+      </c>
+      <c r="U39">
         <v>4.39</v>
       </c>
-      <c r="U39">
-        <v>0</v>
-      </c>
       <c r="V39">
+        <v>0</v>
+      </c>
+      <c r="W39">
         <v>4.31</v>
       </c>
-      <c r="W39">
-        <v>0</v>
-      </c>
       <c r="X39">
+        <v>0</v>
+      </c>
+      <c r="Y39">
         <v>22.06</v>
       </c>
-      <c r="Y39">
-        <v>0</v>
-      </c>
       <c r="Z39">
+        <v>0</v>
+      </c>
+      <c r="AA39">
         <v>0.6</v>
       </c>
-      <c r="AA39">
-        <v>0</v>
-      </c>
       <c r="AB39">
+        <v>0</v>
+      </c>
+      <c r="AC39">
         <v>6.18</v>
       </c>
-      <c r="AC39">
-        <v>0</v>
-      </c>
       <c r="AD39">
+        <v>0</v>
+      </c>
+      <c r="AE39">
         <v>3.2</v>
       </c>
-      <c r="AE39">
-        <v>0</v>
-      </c>
       <c r="AF39">
         <v>0</v>
       </c>
@@ -6262,11 +6291,11 @@
         <v>0</v>
       </c>
       <c r="AH39">
+        <v>0</v>
+      </c>
+      <c r="AI39">
         <v>-1</v>
       </c>
-      <c r="AI39">
-        <v>0</v>
-      </c>
       <c r="AJ39">
         <v>0</v>
       </c>
@@ -6294,39 +6323,35 @@
       <c r="AR39">
         <v>0</v>
       </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>İşgücü Nisan</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C40">
+      <c r="AS39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:45">
+      <c r="A40" t="s">
+        <v>89</v>
+      </c>
+      <c r="C40" t="s">
+        <v>50</v>
+      </c>
+      <c r="D40">
         <v>45625.87</v>
       </c>
-      <c r="D40">
+      <c r="E40">
         <v>0.43</v>
       </c>
-      <c r="E40">
-        <v>0</v>
-      </c>
       <c r="F40">
+        <v>0</v>
+      </c>
+      <c r="G40">
         <v>0.2</v>
       </c>
-      <c r="G40">
-        <v>0</v>
-      </c>
       <c r="H40">
+        <v>0</v>
+      </c>
+      <c r="I40">
         <v>18.72</v>
       </c>
-      <c r="I40">
-        <v>0</v>
-      </c>
       <c r="J40">
         <v>0</v>
       </c>
@@ -6334,65 +6359,65 @@
         <v>0</v>
       </c>
       <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
         <v>0.15</v>
       </c>
-      <c r="M40">
-        <v>0</v>
-      </c>
       <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
         <v>11.98</v>
       </c>
-      <c r="O40">
-        <v>0</v>
-      </c>
       <c r="P40">
+        <v>0</v>
+      </c>
+      <c r="Q40">
         <v>6.05</v>
       </c>
-      <c r="Q40">
-        <v>0</v>
-      </c>
       <c r="R40">
+        <v>0</v>
+      </c>
+      <c r="S40">
         <v>6.05</v>
       </c>
-      <c r="S40">
-        <v>0</v>
-      </c>
       <c r="T40">
+        <v>0</v>
+      </c>
+      <c r="U40">
         <v>4.39</v>
       </c>
-      <c r="U40">
-        <v>0</v>
-      </c>
       <c r="V40">
+        <v>0</v>
+      </c>
+      <c r="W40">
         <v>4.31</v>
       </c>
-      <c r="W40">
-        <v>0</v>
-      </c>
       <c r="X40">
+        <v>0</v>
+      </c>
+      <c r="Y40">
         <v>11.98</v>
       </c>
-      <c r="Y40">
-        <v>0</v>
-      </c>
       <c r="Z40">
+        <v>0</v>
+      </c>
+      <c r="AA40">
         <v>32.4</v>
       </c>
-      <c r="AA40">
-        <v>0</v>
-      </c>
       <c r="AB40">
+        <v>0</v>
+      </c>
+      <c r="AC40">
         <v>8.34</v>
       </c>
-      <c r="AC40">
-        <v>0</v>
-      </c>
       <c r="AD40">
+        <v>0</v>
+      </c>
+      <c r="AE40">
         <v>11.8</v>
       </c>
-      <c r="AE40">
-        <v>0</v>
-      </c>
       <c r="AF40">
         <v>0</v>
       </c>
@@ -6403,11 +6428,11 @@
         <v>0</v>
       </c>
       <c r="AI40">
+        <v>0</v>
+      </c>
+      <c r="AJ40">
         <v>-1</v>
       </c>
-      <c r="AJ40">
-        <v>0</v>
-      </c>
       <c r="AK40">
         <v>0</v>
       </c>
@@ -6432,105 +6457,101 @@
       <c r="AR40">
         <v>0</v>
       </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>İşgücü Mayıs</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C41">
+      <c r="AS40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:45">
+      <c r="A41" t="s">
+        <v>90</v>
+      </c>
+      <c r="C41" t="s">
+        <v>50</v>
+      </c>
+      <c r="D41">
         <v>45625.87</v>
       </c>
-      <c r="D41">
+      <c r="E41">
         <v>0.18</v>
       </c>
-      <c r="E41">
-        <v>0</v>
-      </c>
       <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
         <v>0.8100000000000001</v>
       </c>
-      <c r="G41">
-        <v>0</v>
-      </c>
       <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
         <v>18.72</v>
       </c>
-      <c r="I41">
-        <v>0</v>
-      </c>
       <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
         <v>0.15</v>
       </c>
-      <c r="K41">
-        <v>0</v>
-      </c>
       <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
         <v>0.1</v>
       </c>
-      <c r="M41">
-        <v>0</v>
-      </c>
       <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
         <v>28.4</v>
       </c>
-      <c r="O41">
-        <v>0</v>
-      </c>
       <c r="P41">
+        <v>0</v>
+      </c>
+      <c r="Q41">
         <v>4.13</v>
       </c>
-      <c r="Q41">
-        <v>0</v>
-      </c>
       <c r="R41">
+        <v>0</v>
+      </c>
+      <c r="S41">
         <v>4.13</v>
       </c>
-      <c r="S41">
-        <v>0</v>
-      </c>
       <c r="T41">
+        <v>0</v>
+      </c>
+      <c r="U41">
         <v>21.39</v>
       </c>
-      <c r="U41">
-        <v>0</v>
-      </c>
       <c r="V41">
+        <v>0</v>
+      </c>
+      <c r="W41">
         <v>1.65</v>
       </c>
-      <c r="W41">
-        <v>0</v>
-      </c>
       <c r="X41">
+        <v>0</v>
+      </c>
+      <c r="Y41">
         <v>28.4</v>
       </c>
-      <c r="Y41">
-        <v>0</v>
-      </c>
       <c r="Z41">
+        <v>0</v>
+      </c>
+      <c r="AA41">
         <v>13.5</v>
       </c>
-      <c r="AA41">
-        <v>0</v>
-      </c>
       <c r="AB41">
+        <v>0</v>
+      </c>
+      <c r="AC41">
         <v>2.72</v>
       </c>
-      <c r="AC41">
-        <v>0</v>
-      </c>
       <c r="AD41">
+        <v>0</v>
+      </c>
+      <c r="AE41">
         <v>4.5</v>
       </c>
-      <c r="AE41">
-        <v>0</v>
-      </c>
       <c r="AF41">
         <v>0</v>
       </c>
@@ -6544,11 +6565,11 @@
         <v>0</v>
       </c>
       <c r="AJ41">
+        <v>0</v>
+      </c>
+      <c r="AK41">
         <v>-1</v>
       </c>
-      <c r="AK41">
-        <v>0</v>
-      </c>
       <c r="AL41">
         <v>0</v>
       </c>
@@ -6570,105 +6591,101 @@
       <c r="AR41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>İşgücü Haziran</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C42">
+      <c r="AS41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:45">
+      <c r="A42" t="s">
+        <v>91</v>
+      </c>
+      <c r="C42" t="s">
+        <v>50</v>
+      </c>
+      <c r="D42">
         <v>45625.87</v>
       </c>
-      <c r="D42">
+      <c r="E42">
         <v>6.76</v>
       </c>
-      <c r="E42">
-        <v>0</v>
-      </c>
       <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
         <v>0.82</v>
       </c>
-      <c r="G42">
-        <v>0</v>
-      </c>
       <c r="H42">
+        <v>0</v>
+      </c>
+      <c r="I42">
         <v>18.72</v>
       </c>
-      <c r="I42">
-        <v>0</v>
-      </c>
       <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
         <v>0.57</v>
       </c>
-      <c r="K42">
-        <v>0</v>
-      </c>
       <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
         <v>0.57</v>
       </c>
-      <c r="M42">
-        <v>0</v>
-      </c>
       <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
         <v>26.54</v>
       </c>
-      <c r="O42">
-        <v>0</v>
-      </c>
       <c r="P42">
+        <v>0</v>
+      </c>
+      <c r="Q42">
         <v>6.5</v>
       </c>
-      <c r="Q42">
-        <v>0</v>
-      </c>
       <c r="R42">
+        <v>0</v>
+      </c>
+      <c r="S42">
         <v>6.05</v>
       </c>
-      <c r="S42">
-        <v>0</v>
-      </c>
       <c r="T42">
+        <v>0</v>
+      </c>
+      <c r="U42">
         <v>40.17</v>
       </c>
-      <c r="U42">
-        <v>0</v>
-      </c>
       <c r="V42">
+        <v>0</v>
+      </c>
+      <c r="W42">
         <v>24.9</v>
       </c>
-      <c r="W42">
-        <v>0</v>
-      </c>
       <c r="X42">
+        <v>0</v>
+      </c>
+      <c r="Y42">
         <v>26.54</v>
       </c>
-      <c r="Y42">
-        <v>0</v>
-      </c>
       <c r="Z42">
+        <v>0</v>
+      </c>
+      <c r="AA42">
         <v>36.5</v>
       </c>
-      <c r="AA42">
-        <v>0</v>
-      </c>
       <c r="AB42">
+        <v>0</v>
+      </c>
+      <c r="AC42">
         <v>2.72</v>
       </c>
-      <c r="AC42">
-        <v>0</v>
-      </c>
       <c r="AD42">
+        <v>0</v>
+      </c>
+      <c r="AE42">
         <v>23.6</v>
       </c>
-      <c r="AE42">
-        <v>0</v>
-      </c>
       <c r="AF42">
         <v>0</v>
       </c>
@@ -6685,11 +6702,11 @@
         <v>0</v>
       </c>
       <c r="AK42">
+        <v>0</v>
+      </c>
+      <c r="AL42">
         <v>-1</v>
       </c>
-      <c r="AL42">
-        <v>0</v>
-      </c>
       <c r="AM42">
         <v>0</v>
       </c>
@@ -6708,33 +6725,29 @@
       <c r="AR42">
         <v>0</v>
       </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>İşgücü Temmuz</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C43">
+      <c r="AS42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:45">
+      <c r="A43" t="s">
+        <v>92</v>
+      </c>
+      <c r="C43" t="s">
+        <v>50</v>
+      </c>
+      <c r="D43">
         <v>45625.87</v>
       </c>
-      <c r="D43">
+      <c r="E43">
         <v>3.09</v>
       </c>
-      <c r="E43">
-        <v>0</v>
-      </c>
       <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
         <v>0.4</v>
       </c>
-      <c r="G43">
-        <v>0</v>
-      </c>
       <c r="H43">
         <v>0</v>
       </c>
@@ -6742,71 +6755,71 @@
         <v>0</v>
       </c>
       <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
         <v>7.31</v>
       </c>
-      <c r="K43">
-        <v>0</v>
-      </c>
       <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
         <v>7.31</v>
       </c>
-      <c r="M43">
-        <v>0</v>
-      </c>
       <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43">
         <v>9.890000000000001</v>
       </c>
-      <c r="O43">
-        <v>0</v>
-      </c>
       <c r="P43">
+        <v>0</v>
+      </c>
+      <c r="Q43">
         <v>13.27</v>
       </c>
-      <c r="Q43">
-        <v>0</v>
-      </c>
       <c r="R43">
+        <v>0</v>
+      </c>
+      <c r="S43">
         <v>13.27</v>
       </c>
-      <c r="S43">
-        <v>0</v>
-      </c>
       <c r="T43">
+        <v>0</v>
+      </c>
+      <c r="U43">
         <v>40.17</v>
       </c>
-      <c r="U43">
-        <v>0</v>
-      </c>
       <c r="V43">
+        <v>0</v>
+      </c>
+      <c r="W43">
         <v>24.9</v>
       </c>
-      <c r="W43">
-        <v>0</v>
-      </c>
       <c r="X43">
+        <v>0</v>
+      </c>
+      <c r="Y43">
         <v>9.890000000000001</v>
       </c>
-      <c r="Y43">
-        <v>0</v>
-      </c>
       <c r="Z43">
+        <v>0</v>
+      </c>
+      <c r="AA43">
         <v>30.6</v>
       </c>
-      <c r="AA43">
-        <v>0</v>
-      </c>
       <c r="AB43">
+        <v>0</v>
+      </c>
+      <c r="AC43">
         <v>2.72</v>
       </c>
-      <c r="AC43">
-        <v>0</v>
-      </c>
       <c r="AD43">
+        <v>0</v>
+      </c>
+      <c r="AE43">
         <v>17.1</v>
       </c>
-      <c r="AE43">
-        <v>0</v>
-      </c>
       <c r="AF43">
         <v>0</v>
       </c>
@@ -6826,11 +6839,11 @@
         <v>0</v>
       </c>
       <c r="AL43">
+        <v>0</v>
+      </c>
+      <c r="AM43">
         <v>-1</v>
       </c>
-      <c r="AM43">
-        <v>0</v>
-      </c>
       <c r="AN43">
         <v>0</v>
       </c>
@@ -6846,24 +6859,20 @@
       <c r="AR43">
         <v>0</v>
       </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>İşgücü Ağustos</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C44">
+      <c r="AS43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:45">
+      <c r="A44" t="s">
+        <v>93</v>
+      </c>
+      <c r="C44" t="s">
+        <v>50</v>
+      </c>
+      <c r="D44">
         <v>45625.87</v>
       </c>
-      <c r="D44">
-        <v>0</v>
-      </c>
       <c r="E44">
         <v>0</v>
       </c>
@@ -6892,59 +6901,59 @@
         <v>0</v>
       </c>
       <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
         <v>12.76</v>
       </c>
-      <c r="O44">
-        <v>0</v>
-      </c>
       <c r="P44">
+        <v>0</v>
+      </c>
+      <c r="Q44">
         <v>6.5</v>
       </c>
-      <c r="Q44">
-        <v>0</v>
-      </c>
       <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44">
         <v>6.05</v>
       </c>
-      <c r="S44">
-        <v>0</v>
-      </c>
       <c r="T44">
+        <v>0</v>
+      </c>
+      <c r="U44">
         <v>40.17</v>
       </c>
-      <c r="U44">
-        <v>0</v>
-      </c>
       <c r="V44">
+        <v>0</v>
+      </c>
+      <c r="W44">
         <v>24.9</v>
       </c>
-      <c r="W44">
-        <v>0</v>
-      </c>
       <c r="X44">
+        <v>0</v>
+      </c>
+      <c r="Y44">
         <v>12.76</v>
       </c>
-      <c r="Y44">
-        <v>0</v>
-      </c>
       <c r="Z44">
+        <v>0</v>
+      </c>
+      <c r="AA44">
         <v>2.1</v>
       </c>
-      <c r="AA44">
-        <v>0</v>
-      </c>
       <c r="AB44">
+        <v>0</v>
+      </c>
+      <c r="AC44">
         <v>2.72</v>
       </c>
-      <c r="AC44">
-        <v>0</v>
-      </c>
       <c r="AD44">
+        <v>0</v>
+      </c>
+      <c r="AE44">
         <v>4.9</v>
       </c>
-      <c r="AE44">
-        <v>0</v>
-      </c>
       <c r="AF44">
         <v>0</v>
       </c>
@@ -6967,11 +6976,11 @@
         <v>0</v>
       </c>
       <c r="AM44">
+        <v>0</v>
+      </c>
+      <c r="AN44">
         <v>-1</v>
       </c>
-      <c r="AN44">
-        <v>0</v>
-      </c>
       <c r="AO44">
         <v>0</v>
       </c>
@@ -6984,24 +6993,20 @@
       <c r="AR44">
         <v>0</v>
       </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>İşgücü Eylül</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C45">
+      <c r="AS44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:45">
+      <c r="A45" t="s">
+        <v>94</v>
+      </c>
+      <c r="C45" t="s">
+        <v>50</v>
+      </c>
+      <c r="D45">
         <v>45625.87</v>
       </c>
-      <c r="D45">
-        <v>0</v>
-      </c>
       <c r="E45">
         <v>0</v>
       </c>
@@ -7030,23 +7035,23 @@
         <v>0</v>
       </c>
       <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
         <v>15.87</v>
       </c>
-      <c r="O45">
-        <v>0</v>
-      </c>
       <c r="P45">
+        <v>0</v>
+      </c>
+      <c r="Q45">
         <v>27.55</v>
       </c>
-      <c r="Q45">
-        <v>0</v>
-      </c>
       <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45">
         <v>27.55</v>
       </c>
-      <c r="S45">
-        <v>0</v>
-      </c>
       <c r="T45">
         <v>0</v>
       </c>
@@ -7060,11 +7065,11 @@
         <v>0</v>
       </c>
       <c r="X45">
+        <v>0</v>
+      </c>
+      <c r="Y45">
         <v>15.87</v>
       </c>
-      <c r="Y45">
-        <v>0</v>
-      </c>
       <c r="Z45">
         <v>0</v>
       </c>
@@ -7072,17 +7077,17 @@
         <v>0</v>
       </c>
       <c r="AB45">
+        <v>0</v>
+      </c>
+      <c r="AC45">
         <v>31.79</v>
       </c>
-      <c r="AC45">
-        <v>0</v>
-      </c>
       <c r="AD45">
+        <v>0</v>
+      </c>
+      <c r="AE45">
         <v>14.75</v>
       </c>
-      <c r="AE45">
-        <v>0</v>
-      </c>
       <c r="AF45">
         <v>0</v>
       </c>
@@ -7108,11 +7113,11 @@
         <v>0</v>
       </c>
       <c r="AN45">
+        <v>0</v>
+      </c>
+      <c r="AO45">
         <v>-1</v>
       </c>
-      <c r="AO45">
-        <v>0</v>
-      </c>
       <c r="AP45">
         <v>0</v>
       </c>
@@ -7122,33 +7127,29 @@
       <c r="AR45">
         <v>0</v>
       </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>İşgücü Ekim</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C46">
+      <c r="AS45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:45">
+      <c r="A46" t="s">
+        <v>95</v>
+      </c>
+      <c r="C46" t="s">
+        <v>50</v>
+      </c>
+      <c r="D46">
         <v>45625.87</v>
       </c>
-      <c r="D46">
+      <c r="E46">
         <v>0.5</v>
       </c>
-      <c r="E46">
-        <v>0</v>
-      </c>
       <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
         <v>0.51</v>
       </c>
-      <c r="G46">
-        <v>0</v>
-      </c>
       <c r="H46">
         <v>0</v>
       </c>
@@ -7168,11 +7169,11 @@
         <v>0</v>
       </c>
       <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
         <v>18.75</v>
       </c>
-      <c r="O46">
-        <v>0</v>
-      </c>
       <c r="P46">
         <v>0</v>
       </c>
@@ -7198,11 +7199,11 @@
         <v>0</v>
       </c>
       <c r="X46">
+        <v>0</v>
+      </c>
+      <c r="Y46">
         <v>18.75</v>
       </c>
-      <c r="Y46">
-        <v>0</v>
-      </c>
       <c r="Z46">
         <v>0</v>
       </c>
@@ -7210,11 +7211,11 @@
         <v>0</v>
       </c>
       <c r="AB46">
+        <v>0</v>
+      </c>
+      <c r="AC46">
         <v>20.88</v>
       </c>
-      <c r="AC46">
-        <v>0</v>
-      </c>
       <c r="AD46">
         <v>0</v>
       </c>
@@ -7249,62 +7250,58 @@
         <v>0</v>
       </c>
       <c r="AO46">
+        <v>0</v>
+      </c>
+      <c r="AP46">
         <v>-1</v>
       </c>
-      <c r="AP46">
-        <v>0</v>
-      </c>
       <c r="AQ46">
         <v>0</v>
       </c>
       <c r="AR46">
         <v>0</v>
       </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>İşgücü Kasım</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C47">
+      <c r="AS46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:45">
+      <c r="A47" t="s">
+        <v>96</v>
+      </c>
+      <c r="C47" t="s">
+        <v>50</v>
+      </c>
+      <c r="D47">
         <v>33796.94</v>
       </c>
-      <c r="D47">
+      <c r="E47">
         <v>0.45</v>
       </c>
-      <c r="E47">
-        <v>0</v>
-      </c>
       <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
         <v>0.63</v>
       </c>
-      <c r="G47">
-        <v>0</v>
-      </c>
       <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
         <v>24.84</v>
       </c>
-      <c r="I47">
-        <v>0</v>
-      </c>
       <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
         <v>0.37</v>
       </c>
-      <c r="K47">
-        <v>0</v>
-      </c>
       <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
         <v>0.37</v>
       </c>
-      <c r="M47">
-        <v>0</v>
-      </c>
       <c r="N47">
         <v>0</v>
       </c>
@@ -7390,32 +7387,28 @@
         <v>0</v>
       </c>
       <c r="AP47">
+        <v>0</v>
+      </c>
+      <c r="AQ47">
         <v>-1</v>
       </c>
-      <c r="AQ47">
-        <v>0</v>
-      </c>
       <c r="AR47">
         <v>0</v>
       </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>İşgücü Aralık</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C48">
+      <c r="AS47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:45">
+      <c r="A48" t="s">
+        <v>97</v>
+      </c>
+      <c r="C48" t="s">
+        <v>50</v>
+      </c>
+      <c r="D48">
         <v>28727.4</v>
       </c>
-      <c r="D48">
-        <v>0</v>
-      </c>
       <c r="E48">
         <v>0</v>
       </c>
@@ -7426,11 +7419,11 @@
         <v>0</v>
       </c>
       <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
         <v>24.16</v>
       </c>
-      <c r="I48">
-        <v>0</v>
-      </c>
       <c r="J48">
         <v>0</v>
       </c>
@@ -7486,11 +7479,11 @@
         <v>0</v>
       </c>
       <c r="AB48">
+        <v>0</v>
+      </c>
+      <c r="AC48">
         <v>4.5</v>
       </c>
-      <c r="AC48">
-        <v>0</v>
-      </c>
       <c r="AD48">
         <v>0</v>
       </c>
@@ -7531,112 +7524,108 @@
         <v>0</v>
       </c>
       <c r="AQ48">
+        <v>0</v>
+      </c>
+      <c r="AR48">
         <v>-1</v>
       </c>
-      <c r="AR48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>İşletme Sermayesi</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C49">
+      <c r="AS48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:45">
+      <c r="A49" t="s">
+        <v>98</v>
+      </c>
+      <c r="C49" t="s">
+        <v>50</v>
+      </c>
+      <c r="D49">
         <v>10184195908.55</v>
       </c>
-      <c r="D49">
+      <c r="E49">
         <v>324.12</v>
       </c>
-      <c r="E49">
-        <v>0</v>
-      </c>
       <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
         <v>839.12</v>
       </c>
-      <c r="G49">
-        <v>0</v>
-      </c>
       <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
         <v>1439.82</v>
       </c>
-      <c r="I49">
-        <v>0</v>
-      </c>
       <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
         <v>292.92</v>
       </c>
-      <c r="K49">
-        <v>0</v>
-      </c>
       <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
         <v>721.12</v>
       </c>
-      <c r="M49">
-        <v>0</v>
-      </c>
       <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
         <v>1935.27</v>
       </c>
-      <c r="O49">
-        <v>0</v>
-      </c>
       <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49">
         <v>2710.05</v>
       </c>
-      <c r="Q49">
-        <v>0</v>
-      </c>
       <c r="R49">
+        <v>0</v>
+      </c>
+      <c r="S49">
         <v>2166.68</v>
       </c>
-      <c r="S49">
-        <v>0</v>
-      </c>
       <c r="T49">
+        <v>0</v>
+      </c>
+      <c r="U49">
         <v>8502.950000000001</v>
       </c>
-      <c r="U49">
-        <v>0</v>
-      </c>
       <c r="V49">
+        <v>0</v>
+      </c>
+      <c r="W49">
         <v>5892.95</v>
       </c>
-      <c r="W49">
-        <v>0</v>
-      </c>
       <c r="X49">
+        <v>0</v>
+      </c>
+      <c r="Y49">
         <v>7597.45</v>
       </c>
-      <c r="Y49">
-        <v>0</v>
-      </c>
       <c r="Z49">
+        <v>0</v>
+      </c>
+      <c r="AA49">
         <v>6173.95</v>
       </c>
-      <c r="AA49">
-        <v>0</v>
-      </c>
       <c r="AB49">
+        <v>0</v>
+      </c>
+      <c r="AC49">
         <v>3040</v>
       </c>
-      <c r="AC49">
-        <v>0</v>
-      </c>
       <c r="AD49">
+        <v>0</v>
+      </c>
+      <c r="AE49">
         <v>1004.65</v>
       </c>
-      <c r="AE49">
-        <v>0</v>
-      </c>
       <c r="AF49">
-        <v>18.75</v>
+        <v>0</v>
       </c>
       <c r="AG49">
         <v>18.75</v>
@@ -7672,22 +7661,18 @@
         <v>18.75</v>
       </c>
       <c r="AR49">
+        <v>18.75</v>
+      </c>
+      <c r="AS49">
         <v>-1</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Ahır Yeri</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C50">
-        <v>0</v>
+    <row r="50" spans="1:45">
+      <c r="A50" t="s">
+        <v>99</v>
+      </c>
+      <c r="C50" t="s">
+        <v>50</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -7812,20 +7797,16 @@
       <c r="AR50">
         <v>0</v>
       </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Ağıl Yeri</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="C51">
-        <v>0</v>
+      <c r="AS50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:45">
+      <c r="A51" t="s">
+        <v>100</v>
+      </c>
+      <c r="C51" t="s">
+        <v>50</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -7948,6 +7929,9 @@
         <v>0</v>
       </c>
       <c r="AR51">
+        <v>0</v>
+      </c>
+      <c r="AS51">
         <v>0</v>
       </c>
     </row>
@@ -7965,38 +7949,28 @@
     <col min="2" max="2" width="17.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>101</v>
       </c>
       <c r="B1">
         <v>185267649.936</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>code</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>OPTIMAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Solution is optimal</t>
-        </is>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -8018,48 +7992,32 @@
     <col min="7" max="7" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>variable</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>reduced_cost</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>original_value</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>lower_bound</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>upper_bound</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>is_basic_variable</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Buğday, Durum Buğdayı Hariç</t>
-        </is>
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>3</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -8080,11 +8038,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Buğday, Durum Buğdayı Hariç Satış</t>
-        </is>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>4</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -8105,11 +8061,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Buğday (Sulu)</t>
-        </is>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>5</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -8130,11 +8084,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Buğday (Sulu) Satış</t>
-        </is>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>6</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -8155,11 +8107,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Mısır (Dane)</t>
-        </is>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>7</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -8180,11 +8130,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Mısır (Dane) Satış</t>
-        </is>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>8</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -8205,11 +8153,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Arpa (Diğer) (Kuru)</t>
-        </is>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>9</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -8230,11 +8176,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Arpa (Diğer) (Kuru) Satış</t>
-        </is>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>10</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -8255,11 +8199,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Arpa (Sulu)</t>
-        </is>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>11</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -8280,11 +8222,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Arpa (Sulu) Satış</t>
-        </is>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>12</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -8305,11 +8245,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Fasulye, Taze</t>
-        </is>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>13</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -8330,11 +8268,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Fasulye, Taze Satış</t>
-        </is>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>14</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -8355,11 +8291,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Karpuz</t>
-        </is>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>15</v>
       </c>
       <c r="B14">
         <v>4992</v>
@@ -8380,11 +8314,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Karpuz Satış</t>
-        </is>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>16</v>
       </c>
       <c r="B15">
         <v>19968000</v>
@@ -8405,11 +8337,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Kavun</t>
-        </is>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>17</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -8430,11 +8360,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Kavun Satış</t>
-        </is>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>18</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -8455,11 +8383,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Biber (Sivri)</t>
-        </is>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>19</v>
       </c>
       <c r="B18">
         <v>922.9</v>
@@ -8480,11 +8406,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Biber (Sivri) Satış</t>
-        </is>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>20</v>
       </c>
       <c r="B19">
         <v>5537400</v>
@@ -8505,11 +8429,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Hıyar (Sofralık)</t>
-        </is>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>21</v>
       </c>
       <c r="B20">
         <v>1101.1</v>
@@ -8530,11 +8452,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Hıyar (Sofralık) Satış</t>
-        </is>
+    <row r="21" spans="1:7">
+      <c r="A21" t="s">
+        <v>22</v>
       </c>
       <c r="B21">
         <v>4954950</v>
@@ -8555,11 +8475,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Patlıcan</t>
-        </is>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>23</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -8580,11 +8498,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Patlıcan Satış</t>
-        </is>
+    <row r="23" spans="1:7">
+      <c r="A23" t="s">
+        <v>24</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -8605,11 +8521,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Domates (Sofralık)</t>
-        </is>
+    <row r="24" spans="1:7">
+      <c r="A24" t="s">
+        <v>25</v>
       </c>
       <c r="B24">
         <v>12311.2</v>
@@ -8630,11 +8544,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Domates (Sofralık) Satış</t>
-        </is>
+    <row r="25" spans="1:7">
+      <c r="A25" t="s">
+        <v>26</v>
       </c>
       <c r="B25">
         <v>62516273.6</v>
@@ -8655,11 +8567,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Elma (Bütünleştirilmiş)</t>
-        </is>
+    <row r="26" spans="1:7">
+      <c r="A26" t="s">
+        <v>27</v>
       </c>
       <c r="B26">
         <v>72783</v>
@@ -8680,11 +8590,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Elma (Bütünleştirilmiş) Satış</t>
-        </is>
+    <row r="27" spans="1:7">
+      <c r="A27" t="s">
+        <v>28</v>
       </c>
       <c r="B27">
         <v>218349000</v>
@@ -8705,11 +8613,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Armut</t>
-        </is>
+    <row r="28" spans="1:7">
+      <c r="A28" t="s">
+        <v>29</v>
       </c>
       <c r="B28">
         <v>686</v>
@@ -8730,11 +8636,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Armut Satış</t>
-        </is>
+    <row r="29" spans="1:7">
+      <c r="A29" t="s">
+        <v>30</v>
       </c>
       <c r="B29">
         <v>672280</v>
@@ -8755,11 +8659,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>İg1</t>
-        </is>
+    <row r="30" spans="1:7">
+      <c r="A30" t="s">
+        <v>31</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -8780,11 +8682,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>İg2</t>
-        </is>
+    <row r="31" spans="1:7">
+      <c r="A31" t="s">
+        <v>32</v>
       </c>
       <c r="B31">
         <v>109762.482</v>
@@ -8805,11 +8705,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>İg3</t>
-        </is>
+    <row r="32" spans="1:7">
+      <c r="A32" t="s">
+        <v>33</v>
       </c>
       <c r="B32">
         <v>434381.192</v>
@@ -8830,11 +8728,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>İg4</t>
-        </is>
+    <row r="33" spans="1:7">
+      <c r="A33" t="s">
+        <v>34</v>
       </c>
       <c r="B33">
         <v>1007360.902</v>
@@ -8855,11 +8751,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>İg5</t>
-        </is>
+    <row r="34" spans="1:7">
+      <c r="A34" t="s">
+        <v>35</v>
       </c>
       <c r="B34">
         <v>363806.696</v>
@@ -8880,11 +8774,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>İg6</t>
-        </is>
+    <row r="35" spans="1:7">
+      <c r="A35" t="s">
+        <v>36</v>
       </c>
       <c r="B35">
         <v>714830.573</v>
@@ -8905,11 +8797,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>İg7</t>
-        </is>
+    <row r="36" spans="1:7">
+      <c r="A36" t="s">
+        <v>37</v>
       </c>
       <c r="B36">
         <v>671531.333</v>
@@ -8930,11 +8820,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>İg8</t>
-        </is>
+    <row r="37" spans="1:7">
+      <c r="A37" t="s">
+        <v>38</v>
       </c>
       <c r="B37">
         <v>278497.093</v>
@@ -8955,11 +8843,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>İg9</t>
-        </is>
+    <row r="38" spans="1:7">
+      <c r="A38" t="s">
+        <v>39</v>
       </c>
       <c r="B38">
         <v>2415793.8</v>
@@ -8980,11 +8866,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>İg10</t>
-        </is>
+    <row r="39" spans="1:7">
+      <c r="A39" t="s">
+        <v>40</v>
       </c>
       <c r="B39">
         <v>1474083.17</v>
@@ -9005,11 +8889,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>İg11</t>
-        </is>
+    <row r="40" spans="1:7">
+      <c r="A40" t="s">
+        <v>41</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -9030,11 +8912,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>İg12</t>
-        </is>
+    <row r="41" spans="1:7">
+      <c r="A41" t="s">
+        <v>42</v>
       </c>
       <c r="B41">
         <v>298796.1</v>
@@ -9055,11 +8935,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Sermaye Temini</t>
-        </is>
+    <row r="42" spans="1:7">
+      <c r="A42" t="s">
+        <v>43</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -9099,48 +8977,32 @@
     <col min="7" max="7" width="23.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>constraint</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>shadow_price</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>slack_or_surplus</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>original_value</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>lower_bound</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>upper_bound</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>neither_bounds_are_binding</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Toplam Arazi</t>
-        </is>
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>49</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -9161,11 +9023,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Toplam Kuru Tarla Arazisi</t>
-        </is>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>51</v>
       </c>
       <c r="B3">
         <v>15.643</v>
@@ -9186,11 +9046,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Toplam Sulu Tarla Arazisi</t>
-        </is>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>52</v>
       </c>
       <c r="B4">
         <v>671.1180000000001</v>
@@ -9211,11 +9069,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Toplam Meyve Arazisi</t>
-        </is>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>53</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -9236,11 +9092,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Toplam Sebze Arazisi</t>
-        </is>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>54</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -9261,11 +9115,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Toplam Örtü Altı Arazisi</t>
-        </is>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>55</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -9286,11 +9138,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Toplam Süs Bitkisi Arazisi</t>
-        </is>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>57</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -9311,11 +9161,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Buğday, Durum Buğdayı Hariç Arazisi</t>
-        </is>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>58</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -9336,11 +9184,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Buğday (Sulu) Arazisi</t>
-        </is>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>59</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -9361,11 +9207,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Mısır (Dane) Arazisi</t>
-        </is>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>60</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -9386,11 +9230,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Arpa (Diğer) (Kuru) Arazisi</t>
-        </is>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>61</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -9411,11 +9253,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Arpa (Sulu) Arazisi</t>
-        </is>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>62</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -9436,11 +9276,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fasulye, Taze Arazisi</t>
-        </is>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>63</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -9461,11 +9299,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Karpuz Arazisi</t>
-        </is>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>64</v>
       </c>
       <c r="B15">
         <v>89.95</v>
@@ -9486,11 +9322,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Kavun Arazisi</t>
-        </is>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>65</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -9511,11 +9345,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Biber (Sivri) Arazisi</t>
-        </is>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>66</v>
       </c>
       <c r="B17">
         <v>2389.488</v>
@@ -9536,11 +9368,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Hıyar (Sofralık) Arazisi</t>
-        </is>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>67</v>
       </c>
       <c r="B18">
         <v>4133.05</v>
@@ -9561,11 +9391,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Patlıcan Arazisi</t>
-        </is>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>68</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -9586,11 +9414,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Domates (Sofralık) Arazisi</t>
-        </is>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>69</v>
       </c>
       <c r="B20">
         <v>279.9</v>
@@ -9611,11 +9437,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Elma (Bütünleştirilmiş) Arazisi</t>
-        </is>
+    <row r="21" spans="1:7">
+      <c r="A21" t="s">
+        <v>70</v>
       </c>
       <c r="B21">
         <v>2280.5</v>
@@ -9636,11 +9460,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Armut Arazisi</t>
-        </is>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>71</v>
       </c>
       <c r="B22">
         <v>1363.788</v>
@@ -9661,11 +9483,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Buğday, Durum Buğdayı Hariç Transfer</t>
-        </is>
+    <row r="23" spans="1:7">
+      <c r="A23" t="s">
+        <v>72</v>
       </c>
       <c r="B23">
         <v>2.73</v>
@@ -9686,11 +9506,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Buğday (Sulu) Transfer</t>
-        </is>
+    <row r="24" spans="1:7">
+      <c r="A24" t="s">
+        <v>73</v>
       </c>
       <c r="B24">
         <v>2.73</v>
@@ -9711,11 +9529,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Mısır (Dane) Transfer</t>
-        </is>
+    <row r="25" spans="1:7">
+      <c r="A25" t="s">
+        <v>74</v>
       </c>
       <c r="B25">
         <v>2.6</v>
@@ -9736,11 +9552,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Arpa (Diğer) (Kuru) Transfer</t>
-        </is>
+    <row r="26" spans="1:7">
+      <c r="A26" t="s">
+        <v>75</v>
       </c>
       <c r="B26">
         <v>2.5</v>
@@ -9761,11 +9575,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Arpa (Sulu) Transfer</t>
-        </is>
+    <row r="27" spans="1:7">
+      <c r="A27" t="s">
+        <v>76</v>
       </c>
       <c r="B27">
         <v>2.5</v>
@@ -9786,11 +9598,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Fasulye, Taze Transfer</t>
-        </is>
+    <row r="28" spans="1:7">
+      <c r="A28" t="s">
+        <v>77</v>
       </c>
       <c r="B28">
         <v>2.5</v>
@@ -9811,11 +9621,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Karpuz Transfer</t>
-        </is>
+    <row r="29" spans="1:7">
+      <c r="A29" t="s">
+        <v>78</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -9836,11 +9644,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Kavun Transfer</t>
-        </is>
+    <row r="30" spans="1:7">
+      <c r="A30" t="s">
+        <v>79</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -9861,11 +9667,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Biber (Sivri) Transfer</t>
-        </is>
+    <row r="31" spans="1:7">
+      <c r="A31" t="s">
+        <v>80</v>
       </c>
       <c r="B31">
         <v>2.3</v>
@@ -9886,11 +9690,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Hıyar (Sofralık) Transfer</t>
-        </is>
+    <row r="32" spans="1:7">
+      <c r="A32" t="s">
+        <v>81</v>
       </c>
       <c r="B32">
         <v>2.6</v>
@@ -9911,11 +9713,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Patlıcan Transfer</t>
-        </is>
+    <row r="33" spans="1:7">
+      <c r="A33" t="s">
+        <v>82</v>
       </c>
       <c r="B33">
         <v>2.2</v>
@@ -9936,11 +9736,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Domates (Sofralık) Transfer</t>
-        </is>
+    <row r="34" spans="1:7">
+      <c r="A34" t="s">
+        <v>83</v>
       </c>
       <c r="B34">
         <v>1.7</v>
@@ -9961,11 +9759,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Elma (Bütünleştirilmiş) Transfer</t>
-        </is>
+    <row r="35" spans="1:7">
+      <c r="A35" t="s">
+        <v>84</v>
       </c>
       <c r="B35">
         <v>2.3</v>
@@ -9986,11 +9782,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Armut Transfer</t>
-        </is>
+    <row r="36" spans="1:7">
+      <c r="A36" t="s">
+        <v>85</v>
       </c>
       <c r="B36">
         <v>4</v>
@@ -10011,11 +9805,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>İşgücü Ocak</t>
-        </is>
+    <row r="37" spans="1:7">
+      <c r="A37" t="s">
+        <v>86</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -10036,11 +9828,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>İşgücü Şubat</t>
-        </is>
+    <row r="38" spans="1:7">
+      <c r="A38" t="s">
+        <v>87</v>
       </c>
       <c r="B38">
         <v>18.75</v>
@@ -10061,11 +9851,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>İşgücü Mart</t>
-        </is>
+    <row r="39" spans="1:7">
+      <c r="A39" t="s">
+        <v>88</v>
       </c>
       <c r="B39">
         <v>18.75</v>
@@ -10086,11 +9874,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>İşgücü Nisan</t>
-        </is>
+    <row r="40" spans="1:7">
+      <c r="A40" t="s">
+        <v>89</v>
       </c>
       <c r="B40">
         <v>18.75</v>
@@ -10111,11 +9897,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>İşgücü Mayıs</t>
-        </is>
+    <row r="41" spans="1:7">
+      <c r="A41" t="s">
+        <v>90</v>
       </c>
       <c r="B41">
         <v>18.75</v>
@@ -10136,11 +9920,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>İşgücü Haziran</t>
-        </is>
+    <row r="42" spans="1:7">
+      <c r="A42" t="s">
+        <v>91</v>
       </c>
       <c r="B42">
         <v>18.75</v>
@@ -10161,11 +9943,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>İşgücü Temmuz</t>
-        </is>
+    <row r="43" spans="1:7">
+      <c r="A43" t="s">
+        <v>92</v>
       </c>
       <c r="B43">
         <v>18.75</v>
@@ -10186,11 +9966,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>İşgücü Ağustos</t>
-        </is>
+    <row r="44" spans="1:7">
+      <c r="A44" t="s">
+        <v>93</v>
       </c>
       <c r="B44">
         <v>18.75</v>
@@ -10211,11 +9989,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>İşgücü Eylül</t>
-        </is>
+    <row r="45" spans="1:7">
+      <c r="A45" t="s">
+        <v>94</v>
       </c>
       <c r="B45">
         <v>18.75</v>
@@ -10236,11 +10012,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>İşgücü Ekim</t>
-        </is>
+    <row r="46" spans="1:7">
+      <c r="A46" t="s">
+        <v>95</v>
       </c>
       <c r="B46">
         <v>18.75</v>
@@ -10261,11 +10035,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>İşgücü Kasım</t>
-        </is>
+    <row r="47" spans="1:7">
+      <c r="A47" t="s">
+        <v>96</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -10286,11 +10058,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>İşgücü Aralık</t>
-        </is>
+    <row r="48" spans="1:7">
+      <c r="A48" t="s">
+        <v>97</v>
       </c>
       <c r="B48">
         <v>18.75</v>
@@ -10311,11 +10081,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>İşletme Sermayesi</t>
-        </is>
+    <row r="49" spans="1:7">
+      <c r="A49" t="s">
+        <v>98</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -10336,11 +10104,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Ahır Yeri</t>
-        </is>
+    <row r="50" spans="1:7">
+      <c r="A50" t="s">
+        <v>99</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -10361,11 +10127,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Ağıl Yeri</t>
-        </is>
+    <row r="51" spans="1:7">
+      <c r="A51" t="s">
+        <v>100</v>
       </c>
       <c r="B51">
         <v>0</v>

--- a/test/integration/03-out.xlsx
+++ b/test/integration/03-out.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="113">
   <si>
     <t>variable</t>
   </si>
@@ -29,6 +29,9 @@
     <t>name</t>
   </si>
   <si>
+    <t>method</t>
+  </si>
+  <si>
     <t>Buğday, Durum Buğdayı Hariç</t>
   </si>
   <si>
@@ -152,9 +155,6 @@
     <t>Sermaye Temini</t>
   </si>
   <si>
-    <t>{}</t>
-  </si>
-  <si>
     <t>constraint</t>
   </si>
   <si>
@@ -164,12 +164,54 @@
     <t>rhs</t>
   </si>
   <si>
+    <t>&lt;=</t>
+  </si>
+  <si>
+    <t>=</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>OPTIMAL</t>
+  </si>
+  <si>
+    <t>Solution is optimal</t>
+  </si>
+  <si>
+    <t>reduced_cost</t>
+  </si>
+  <si>
+    <t>original_value</t>
+  </si>
+  <si>
+    <t>lower_bound</t>
+  </si>
+  <si>
+    <t>upper_bound</t>
+  </si>
+  <si>
+    <t>is_basic_variable</t>
+  </si>
+  <si>
+    <t>shadow_price</t>
+  </si>
+  <si>
+    <t>slack_or_surplus</t>
+  </si>
+  <si>
+    <t>neither_bounds_are_binding</t>
+  </si>
+  <si>
     <t>Toplam Arazi</t>
   </si>
   <si>
-    <t>&lt;=</t>
-  </si>
-  <si>
     <t>Toplam Kuru Tarla Arazisi</t>
   </si>
   <si>
@@ -185,9 +227,6 @@
     <t>Toplam Örtü Altı Arazisi</t>
   </si>
   <si>
-    <t>=</t>
-  </si>
-  <si>
     <t>Toplam Süs Bitkisi Arazisi</t>
   </si>
   <si>
@@ -318,45 +357,6 @@
   </si>
   <si>
     <t>Ağıl Yeri</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>OPTIMAL</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>Solution is optimal</t>
-  </si>
-  <si>
-    <t>reduced_cost</t>
-  </si>
-  <si>
-    <t>original_value</t>
-  </si>
-  <si>
-    <t>lower_bound</t>
-  </si>
-  <si>
-    <t>upper_bound</t>
-  </si>
-  <si>
-    <t>is_basic_variable</t>
-  </si>
-  <si>
-    <t>shadow_price</t>
-  </si>
-  <si>
-    <t>slack_or_surplus</t>
-  </si>
-  <si>
-    <t>neither_bounds_are_binding</t>
   </si>
 </sst>
 </file>
@@ -688,15 +688,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="10.5703125" customWidth="1"/>
     <col min="3" max="3" width="4.42578125" customWidth="1"/>
+    <col min="4" max="4" width="6.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -706,125 +707,125 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>-324.12</v>
       </c>
-      <c r="C2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>2.73</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4">
         <v>-839.12</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5">
         <v>2.73</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6">
         <v>-1439.82</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7">
         <v>2.6</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8">
         <v>-292.92</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9">
         <v>2.5</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10">
         <v>-721.12</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11">
         <v>2.5</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12">
         <v>-1935.27</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B13">
         <v>2.5</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B14">
         <v>-2710.05</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B15">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B16">
         <v>-2166.68</v>
@@ -832,7 +833,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -840,7 +841,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B18">
         <v>-8502.950000000001</v>
@@ -848,7 +849,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B19">
         <v>2.3</v>
@@ -856,7 +857,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B20">
         <v>-5892.95</v>
@@ -864,7 +865,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B21">
         <v>2.6</v>
@@ -872,7 +873,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B22">
         <v>-7597.45</v>
@@ -880,7 +881,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B23">
         <v>2.2</v>
@@ -888,7 +889,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B24">
         <v>-6173.95</v>
@@ -896,7 +897,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B25">
         <v>1.7</v>
@@ -904,7 +905,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B26">
         <v>-3040</v>
@@ -912,7 +913,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B27">
         <v>2.3</v>
@@ -920,7 +921,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B28">
         <v>-1004.65</v>
@@ -928,7 +929,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B29">
         <v>4</v>
@@ -936,7 +937,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B30">
         <v>-18.75</v>
@@ -944,7 +945,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B31">
         <v>-18.75</v>
@@ -952,7 +953,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B32">
         <v>-18.75</v>
@@ -960,7 +961,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B33">
         <v>-18.75</v>
@@ -968,7 +969,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B34">
         <v>-18.75</v>
@@ -976,7 +977,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B35">
         <v>-18.75</v>
@@ -984,7 +985,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B36">
         <v>-18.75</v>
@@ -992,7 +993,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B37">
         <v>-18.75</v>
@@ -1000,7 +1001,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B38">
         <v>-18.75</v>
@@ -1008,7 +1009,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B39">
         <v>-18.75</v>
@@ -1016,7 +1017,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B40">
         <v>-18.75</v>
@@ -1024,7 +1025,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B41">
         <v>-18.75</v>
@@ -1032,7 +1033,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B42">
         <v>-0.25</v>
@@ -1048,7 +1049,7 @@
   <dimension ref="A1:AR51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="32.5703125" customWidth="1"/>
+    <col min="1" max="1" width="9.7109375" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="3.5703125" customWidth="1"/>
     <col min="4" max="4" width="24.7109375" customWidth="1"/>
@@ -1105,135 +1106,132 @@
         <v>47</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Q1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="U1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="W1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="X1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Z1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AB1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AC1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AD1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AF1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AG1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AH1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AI1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AJ1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AK1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AL1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AM1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AN1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AO1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="AP1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AQ1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AR1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:44">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>48</v>
-      </c>
-      <c r="B2" t="s">
-        <v>49</v>
       </c>
       <c r="C2">
         <v>5508331</v>
@@ -1363,11 +1361,8 @@
       </c>
     </row>
     <row r="3" spans="1:44">
-      <c r="A3" t="s">
-        <v>50</v>
-      </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1497,11 +1492,8 @@
       </c>
     </row>
     <row r="4" spans="1:44">
-      <c r="A4" t="s">
-        <v>51</v>
-      </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1631,11 +1623,8 @@
       </c>
     </row>
     <row r="5" spans="1:44">
-      <c r="A5" t="s">
-        <v>52</v>
-      </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C5">
         <v>154013</v>
@@ -1765,11 +1754,8 @@
       </c>
     </row>
     <row r="6" spans="1:44">
-      <c r="A6" t="s">
-        <v>53</v>
-      </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C6">
         <v>397158</v>
@@ -1899,11 +1885,8 @@
       </c>
     </row>
     <row r="7" spans="1:44">
-      <c r="A7" t="s">
-        <v>54</v>
-      </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -2033,11 +2016,8 @@
       </c>
     </row>
     <row r="8" spans="1:44">
-      <c r="A8" t="s">
-        <v>56</v>
-      </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -2167,11 +2147,8 @@
       </c>
     </row>
     <row r="9" spans="1:44">
-      <c r="A9" t="s">
-        <v>57</v>
-      </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C9">
         <v>2189475</v>
@@ -2301,11 +2278,8 @@
       </c>
     </row>
     <row r="10" spans="1:44">
-      <c r="A10" t="s">
-        <v>58</v>
-      </c>
       <c r="B10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C10">
         <v>279382.5</v>
@@ -2435,11 +2409,8 @@
       </c>
     </row>
     <row r="11" spans="1:44">
-      <c r="A11" t="s">
-        <v>59</v>
-      </c>
       <c r="B11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C11">
         <v>13156.5</v>
@@ -2569,11 +2540,8 @@
       </c>
     </row>
     <row r="12" spans="1:44">
-      <c r="A12" t="s">
-        <v>60</v>
-      </c>
       <c r="B12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C12">
         <v>1359679.5</v>
@@ -2703,11 +2671,8 @@
       </c>
     </row>
     <row r="13" spans="1:44">
-      <c r="A13" t="s">
-        <v>61</v>
-      </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C13">
         <v>87864</v>
@@ -2837,11 +2802,8 @@
       </c>
     </row>
     <row r="14" spans="1:44">
-      <c r="A14" t="s">
-        <v>62</v>
-      </c>
       <c r="B14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C14">
         <v>1962</v>
@@ -2971,11 +2933,8 @@
       </c>
     </row>
     <row r="15" spans="1:44">
-      <c r="A15" t="s">
-        <v>63</v>
-      </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C15">
         <v>4992</v>
@@ -3105,11 +3064,8 @@
       </c>
     </row>
     <row r="16" spans="1:44">
-      <c r="A16" t="s">
-        <v>64</v>
-      </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C16">
         <v>1614</v>
@@ -3238,12 +3194,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:44">
-      <c r="A17" t="s">
-        <v>65</v>
-      </c>
+    <row r="17" spans="2:44">
       <c r="B17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C17">
         <v>922.9</v>
@@ -3372,12 +3325,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:44">
-      <c r="A18" t="s">
-        <v>66</v>
-      </c>
+    <row r="18" spans="2:44">
       <c r="B18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C18">
         <v>1101.1</v>
@@ -3506,12 +3456,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:44">
-      <c r="A19" t="s">
-        <v>67</v>
-      </c>
+    <row r="19" spans="2:44">
       <c r="B19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C19">
         <v>957</v>
@@ -3640,12 +3587,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:44">
-      <c r="A20" t="s">
-        <v>68</v>
-      </c>
+    <row r="20" spans="2:44">
       <c r="B20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C20">
         <v>12311.2</v>
@@ -3774,12 +3718,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:44">
-      <c r="A21" t="s">
-        <v>69</v>
-      </c>
+    <row r="21" spans="2:44">
       <c r="B21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C21">
         <v>72783</v>
@@ -3908,12 +3849,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:44">
-      <c r="A22" t="s">
-        <v>70</v>
-      </c>
+    <row r="22" spans="2:44">
       <c r="B22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C22">
         <v>686</v>
@@ -4042,12 +3980,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:44">
-      <c r="A23" t="s">
-        <v>71</v>
-      </c>
+    <row r="23" spans="2:44">
       <c r="B23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -4176,12 +4111,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:44">
-      <c r="A24" t="s">
-        <v>72</v>
-      </c>
+    <row r="24" spans="2:44">
       <c r="B24" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -4310,12 +4242,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:44">
-      <c r="A25" t="s">
-        <v>73</v>
-      </c>
+    <row r="25" spans="2:44">
       <c r="B25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -4444,12 +4373,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:44">
-      <c r="A26" t="s">
-        <v>74</v>
-      </c>
+    <row r="26" spans="2:44">
       <c r="B26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -4578,12 +4504,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:44">
-      <c r="A27" t="s">
-        <v>75</v>
-      </c>
+    <row r="27" spans="2:44">
       <c r="B27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -4712,12 +4635,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:44">
-      <c r="A28" t="s">
-        <v>76</v>
-      </c>
+    <row r="28" spans="2:44">
       <c r="B28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -4846,12 +4766,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:44">
-      <c r="A29" t="s">
-        <v>77</v>
-      </c>
+    <row r="29" spans="2:44">
       <c r="B29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -4980,12 +4897,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:44">
-      <c r="A30" t="s">
-        <v>78</v>
-      </c>
+    <row r="30" spans="2:44">
       <c r="B30" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -5114,12 +5028,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:44">
-      <c r="A31" t="s">
-        <v>79</v>
-      </c>
+    <row r="31" spans="2:44">
       <c r="B31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -5248,12 +5159,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:44">
-      <c r="A32" t="s">
-        <v>80</v>
-      </c>
+    <row r="32" spans="2:44">
       <c r="B32" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -5382,12 +5290,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:44">
-      <c r="A33" t="s">
-        <v>81</v>
-      </c>
+    <row r="33" spans="2:44">
       <c r="B33" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -5516,12 +5421,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:44">
-      <c r="A34" t="s">
-        <v>82</v>
-      </c>
+    <row r="34" spans="2:44">
       <c r="B34" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -5650,12 +5552,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:44">
-      <c r="A35" t="s">
-        <v>83</v>
-      </c>
+    <row r="35" spans="2:44">
       <c r="B35" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -5784,12 +5683,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:44">
-      <c r="A36" t="s">
-        <v>84</v>
-      </c>
+    <row r="36" spans="2:44">
       <c r="B36" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -5918,12 +5814,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:44">
-      <c r="A37" t="s">
-        <v>85</v>
-      </c>
+    <row r="37" spans="2:44">
       <c r="B37" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C37">
         <v>28727.4</v>
@@ -6052,12 +5945,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:44">
-      <c r="A38" t="s">
-        <v>86</v>
-      </c>
+    <row r="38" spans="2:44">
       <c r="B38" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C38">
         <v>28727.4</v>
@@ -6186,12 +6076,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:44">
-      <c r="A39" t="s">
-        <v>87</v>
-      </c>
+    <row r="39" spans="2:44">
       <c r="B39" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C39">
         <v>33796.94</v>
@@ -6320,12 +6207,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:44">
-      <c r="A40" t="s">
-        <v>88</v>
-      </c>
+    <row r="40" spans="2:44">
       <c r="B40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C40">
         <v>45625.87</v>
@@ -6454,12 +6338,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:44">
-      <c r="A41" t="s">
-        <v>89</v>
-      </c>
+    <row r="41" spans="2:44">
       <c r="B41" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C41">
         <v>45625.87</v>
@@ -6588,12 +6469,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:44">
-      <c r="A42" t="s">
-        <v>90</v>
-      </c>
+    <row r="42" spans="2:44">
       <c r="B42" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C42">
         <v>45625.87</v>
@@ -6722,12 +6600,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:44">
-      <c r="A43" t="s">
-        <v>91</v>
-      </c>
+    <row r="43" spans="2:44">
       <c r="B43" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C43">
         <v>45625.87</v>
@@ -6856,12 +6731,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:44">
-      <c r="A44" t="s">
-        <v>92</v>
-      </c>
+    <row r="44" spans="2:44">
       <c r="B44" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C44">
         <v>45625.87</v>
@@ -6990,12 +6862,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:44">
-      <c r="A45" t="s">
-        <v>93</v>
-      </c>
+    <row r="45" spans="2:44">
       <c r="B45" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C45">
         <v>45625.87</v>
@@ -7124,12 +6993,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:44">
-      <c r="A46" t="s">
-        <v>94</v>
-      </c>
+    <row r="46" spans="2:44">
       <c r="B46" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C46">
         <v>45625.87</v>
@@ -7258,12 +7124,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:44">
-      <c r="A47" t="s">
-        <v>95</v>
-      </c>
+    <row r="47" spans="2:44">
       <c r="B47" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C47">
         <v>33796.94</v>
@@ -7392,12 +7255,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:44">
-      <c r="A48" t="s">
-        <v>96</v>
-      </c>
+    <row r="48" spans="2:44">
       <c r="B48" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C48">
         <v>28727.4</v>
@@ -7526,12 +7386,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:44">
-      <c r="A49" t="s">
-        <v>97</v>
-      </c>
+    <row r="49" spans="2:44">
       <c r="B49" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C49">
         <v>10184195908.55</v>
@@ -7660,12 +7517,9 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="50" spans="1:44">
-      <c r="A50" t="s">
-        <v>98</v>
-      </c>
+    <row r="50" spans="2:44">
       <c r="B50" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C50">
         <v>0</v>
@@ -7794,12 +7648,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:44">
-      <c r="A51" t="s">
-        <v>99</v>
-      </c>
+    <row r="51" spans="2:44">
       <c r="B51" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -7935,35 +7786,34 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" customWidth="1"/>
+    <col min="1" max="1" width="7.140625" customWidth="1"/>
     <col min="2" max="2" width="17.5703125" customWidth="1"/>
+    <col min="3" max="3" width="5.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B1">
+        <v>50</v>
+      </c>
+      <c r="B1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2">
         <v>185267649.936</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B3" t="s">
-        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -7990,27 +7840,27 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="C1" t="s">
-        <v>105</v>
+        <v>55</v>
       </c>
       <c r="D1" t="s">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="E1" t="s">
-        <v>107</v>
+        <v>57</v>
       </c>
       <c r="F1" t="s">
-        <v>108</v>
+        <v>58</v>
       </c>
       <c r="G1" t="s">
-        <v>109</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -8033,7 +7883,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -8056,7 +7906,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -8079,7 +7929,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -8102,7 +7952,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -8125,7 +7975,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -8148,7 +7998,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -8171,7 +8021,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -8194,7 +8044,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -8217,7 +8067,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -8240,7 +8090,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -8263,7 +8113,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -8286,7 +8136,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B14">
         <v>4992</v>
@@ -8309,7 +8159,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B15">
         <v>19968000</v>
@@ -8332,7 +8182,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -8355,7 +8205,7 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -8378,7 +8228,7 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B18">
         <v>922.9</v>
@@ -8401,7 +8251,7 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B19">
         <v>5537400</v>
@@ -8424,7 +8274,7 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B20">
         <v>1101.1</v>
@@ -8447,7 +8297,7 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B21">
         <v>4954950</v>
@@ -8470,7 +8320,7 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -8493,7 +8343,7 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -8516,7 +8366,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B24">
         <v>12311.2</v>
@@ -8539,7 +8389,7 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B25">
         <v>62516273.6</v>
@@ -8562,7 +8412,7 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B26">
         <v>72783</v>
@@ -8585,7 +8435,7 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B27">
         <v>218349000</v>
@@ -8608,7 +8458,7 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B28">
         <v>686</v>
@@ -8631,7 +8481,7 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B29">
         <v>672280</v>
@@ -8654,7 +8504,7 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -8677,7 +8527,7 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B31">
         <v>109762.482</v>
@@ -8700,7 +8550,7 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B32">
         <v>434381.192</v>
@@ -8723,7 +8573,7 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B33">
         <v>1007360.902</v>
@@ -8746,7 +8596,7 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B34">
         <v>363806.696</v>
@@ -8769,7 +8619,7 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B35">
         <v>714830.573</v>
@@ -8792,7 +8642,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B36">
         <v>671531.333</v>
@@ -8815,7 +8665,7 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B37">
         <v>278497.093</v>
@@ -8838,7 +8688,7 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B38">
         <v>2415793.8</v>
@@ -8861,7 +8711,7 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B39">
         <v>1474083.17</v>
@@ -8884,7 +8734,7 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -8907,7 +8757,7 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B41">
         <v>298796.1</v>
@@ -8930,7 +8780,7 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -8975,27 +8825,27 @@
         <v>45</v>
       </c>
       <c r="B1" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="C1" t="s">
-        <v>111</v>
+        <v>61</v>
       </c>
       <c r="D1" t="s">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="E1" t="s">
-        <v>107</v>
+        <v>57</v>
       </c>
       <c r="F1" t="s">
-        <v>108</v>
+        <v>58</v>
       </c>
       <c r="G1" t="s">
-        <v>112</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -9018,7 +8868,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="B3">
         <v>15.643</v>
@@ -9041,7 +8891,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="B4">
         <v>671.1180000000001</v>
@@ -9064,7 +8914,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -9087,7 +8937,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -9110,7 +8960,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -9133,7 +8983,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -9156,7 +9006,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -9179,7 +9029,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -9202,7 +9052,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -9225,7 +9075,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -9248,7 +9098,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -9271,7 +9121,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -9294,7 +9144,7 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="B15">
         <v>89.95</v>
@@ -9317,7 +9167,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -9340,7 +9190,7 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="B17">
         <v>2389.488</v>
@@ -9363,7 +9213,7 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="B18">
         <v>4133.05</v>
@@ -9386,7 +9236,7 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -9409,7 +9259,7 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="B20">
         <v>279.9</v>
@@ -9432,7 +9282,7 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="B21">
         <v>2280.5</v>
@@ -9455,7 +9305,7 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B22">
         <v>1363.788</v>
@@ -9478,7 +9328,7 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B23">
         <v>2.73</v>
@@ -9501,7 +9351,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="B24">
         <v>2.73</v>
@@ -9524,7 +9374,7 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="B25">
         <v>2.6</v>
@@ -9547,7 +9397,7 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="B26">
         <v>2.5</v>
@@ -9570,7 +9420,7 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="B27">
         <v>2.5</v>
@@ -9593,7 +9443,7 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="B28">
         <v>2.5</v>
@@ -9616,7 +9466,7 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -9639,7 +9489,7 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -9662,7 +9512,7 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="B31">
         <v>2.3</v>
@@ -9685,7 +9535,7 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="B32">
         <v>2.6</v>
@@ -9708,7 +9558,7 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="B33">
         <v>2.2</v>
@@ -9731,7 +9581,7 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="B34">
         <v>1.7</v>
@@ -9754,7 +9604,7 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="B35">
         <v>2.3</v>
@@ -9777,7 +9627,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="B36">
         <v>4</v>
@@ -9800,7 +9650,7 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -9823,7 +9673,7 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="B38">
         <v>18.75</v>
@@ -9846,7 +9696,7 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="B39">
         <v>18.75</v>
@@ -9869,7 +9719,7 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="B40">
         <v>18.75</v>
@@ -9892,7 +9742,7 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="B41">
         <v>18.75</v>
@@ -9915,7 +9765,7 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="B42">
         <v>18.75</v>
@@ -9938,7 +9788,7 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="B43">
         <v>18.75</v>
@@ -9961,7 +9811,7 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="B44">
         <v>18.75</v>
@@ -9984,7 +9834,7 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="B45">
         <v>18.75</v>
@@ -10007,7 +9857,7 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="B46">
         <v>18.75</v>
@@ -10030,7 +9880,7 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -10053,7 +9903,7 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="B48">
         <v>18.75</v>
@@ -10076,7 +9926,7 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -10099,7 +9949,7 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -10122,7 +9972,7 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="B51">
         <v>0</v>
